--- a/data/nzd0228/nzd0228.xlsx
+++ b/data/nzd0228/nzd0228.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG297"/>
+  <dimension ref="A1:AG299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31560,11 +31560,221 @@
         <v>518.8200000000001</v>
       </c>
       <c r="AF297" t="n">
-        <v>509.4</v>
+        <v>523.3099999999999</v>
       </c>
       <c r="AG297" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>398.23</v>
+      </c>
+      <c r="C298" t="n">
+        <v>378.5</v>
+      </c>
+      <c r="D298" t="n">
+        <v>381</v>
+      </c>
+      <c r="E298" t="n">
+        <v>387.24</v>
+      </c>
+      <c r="F298" t="n">
+        <v>386.52</v>
+      </c>
+      <c r="G298" t="n">
+        <v>381.81</v>
+      </c>
+      <c r="H298" t="n">
+        <v>383.66</v>
+      </c>
+      <c r="I298" t="n">
+        <v>387</v>
+      </c>
+      <c r="J298" t="n">
+        <v>384.03</v>
+      </c>
+      <c r="K298" t="n">
+        <v>388.57</v>
+      </c>
+      <c r="L298" t="n">
+        <v>394.49</v>
+      </c>
+      <c r="M298" t="n">
+        <v>388.48</v>
+      </c>
+      <c r="N298" t="n">
+        <v>383.24</v>
+      </c>
+      <c r="O298" t="n">
+        <v>388.06</v>
+      </c>
+      <c r="P298" t="n">
+        <v>391.28</v>
+      </c>
+      <c r="Q298" t="n">
+        <v>401.56</v>
+      </c>
+      <c r="R298" t="n">
+        <v>404.9</v>
+      </c>
+      <c r="S298" t="n">
+        <v>407.03</v>
+      </c>
+      <c r="T298" t="n">
+        <v>414.42</v>
+      </c>
+      <c r="U298" t="n">
+        <v>411.06</v>
+      </c>
+      <c r="V298" t="n">
+        <v>391.19</v>
+      </c>
+      <c r="W298" t="n">
+        <v>395.31</v>
+      </c>
+      <c r="X298" t="n">
+        <v>393.28</v>
+      </c>
+      <c r="Y298" t="n">
+        <v>403.39</v>
+      </c>
+      <c r="Z298" t="n">
+        <v>418.39</v>
+      </c>
+      <c r="AA298" t="n">
+        <v>400.36</v>
+      </c>
+      <c r="AB298" t="n">
+        <v>428.99</v>
+      </c>
+      <c r="AC298" t="n">
+        <v>470.97</v>
+      </c>
+      <c r="AD298" t="n">
+        <v>500.61</v>
+      </c>
+      <c r="AE298" t="n">
+        <v>514.29</v>
+      </c>
+      <c r="AF298" t="n">
+        <v>525.54</v>
+      </c>
+      <c r="AG298" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:06:24+00:00</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>394.28</v>
+      </c>
+      <c r="C299" t="n">
+        <v>376.37</v>
+      </c>
+      <c r="D299" t="n">
+        <v>379.76</v>
+      </c>
+      <c r="E299" t="n">
+        <v>384.87</v>
+      </c>
+      <c r="F299" t="n">
+        <v>382.33</v>
+      </c>
+      <c r="G299" t="n">
+        <v>378.08</v>
+      </c>
+      <c r="H299" t="n">
+        <v>379.03</v>
+      </c>
+      <c r="I299" t="n">
+        <v>381.56</v>
+      </c>
+      <c r="J299" t="n">
+        <v>378.8</v>
+      </c>
+      <c r="K299" t="n">
+        <v>383.94</v>
+      </c>
+      <c r="L299" t="n">
+        <v>389.51</v>
+      </c>
+      <c r="M299" t="n">
+        <v>382.83</v>
+      </c>
+      <c r="N299" t="n">
+        <v>379.15</v>
+      </c>
+      <c r="O299" t="n">
+        <v>383.06</v>
+      </c>
+      <c r="P299" t="n">
+        <v>387.28</v>
+      </c>
+      <c r="Q299" t="n">
+        <v>396.17</v>
+      </c>
+      <c r="R299" t="n">
+        <v>398.34</v>
+      </c>
+      <c r="S299" t="n">
+        <v>407.03</v>
+      </c>
+      <c r="T299" t="n">
+        <v>414.42</v>
+      </c>
+      <c r="U299" t="n">
+        <v>411.06</v>
+      </c>
+      <c r="V299" t="n">
+        <v>391.19</v>
+      </c>
+      <c r="W299" t="n">
+        <v>387.19</v>
+      </c>
+      <c r="X299" t="n">
+        <v>385.5</v>
+      </c>
+      <c r="Y299" t="n">
+        <v>395.7</v>
+      </c>
+      <c r="Z299" t="n">
+        <v>408.66</v>
+      </c>
+      <c r="AA299" t="n">
+        <v>390.35</v>
+      </c>
+      <c r="AB299" t="n">
+        <v>415.31</v>
+      </c>
+      <c r="AC299" t="n">
+        <v>457.4</v>
+      </c>
+      <c r="AD299" t="n">
+        <v>490.95</v>
+      </c>
+      <c r="AE299" t="n">
+        <v>508.11</v>
+      </c>
+      <c r="AF299" t="n">
+        <v>521.11</v>
+      </c>
+      <c r="AG299" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -31579,7 +31789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B308"/>
+  <dimension ref="A1:B310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34662,6 +34872,26 @@
       </c>
       <c r="B308" t="n">
         <v>1.67</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>0.28</v>
       </c>
     </row>
   </sheetData>
@@ -34830,28 +35060,28 @@
         <v>0.0389</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4398056881527824</v>
+        <v>-0.4412856762858344</v>
       </c>
       <c r="J2" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K2" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1480916884863784</v>
+        <v>0.1505824832746762</v>
       </c>
       <c r="M2" t="n">
-        <v>5.701272291660792</v>
+        <v>5.674797436039861</v>
       </c>
       <c r="N2" t="n">
-        <v>60.97066251515318</v>
+        <v>60.59508486106192</v>
       </c>
       <c r="O2" t="n">
-        <v>7.808371310020623</v>
+        <v>7.78428447971051</v>
       </c>
       <c r="P2" t="n">
-        <v>408.934526818898</v>
+        <v>408.9500283603307</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34908,28 +35138,28 @@
         <v>0.0413</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9218604940443194</v>
+        <v>-0.9289064068381815</v>
       </c>
       <c r="J3" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K3" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3154674158460291</v>
+        <v>0.321241913616639</v>
       </c>
       <c r="M3" t="n">
-        <v>7.821632518294449</v>
+        <v>7.796706450916592</v>
       </c>
       <c r="N3" t="n">
-        <v>101.0431983892131</v>
+        <v>100.5721436944666</v>
       </c>
       <c r="O3" t="n">
-        <v>10.05202459155434</v>
+        <v>10.02856638281198</v>
       </c>
       <c r="P3" t="n">
-        <v>407.1040663088145</v>
+        <v>407.1778070509299</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34986,28 +35216,28 @@
         <v>0.0432</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.060207266862897</v>
+        <v>-1.067452442010383</v>
       </c>
       <c r="J4" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K4" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3673164187930792</v>
+        <v>0.3731545630570691</v>
       </c>
       <c r="M4" t="n">
-        <v>8.612700959684869</v>
+        <v>8.596286642204349</v>
       </c>
       <c r="N4" t="n">
-        <v>106.0876515874684</v>
+        <v>105.589263503776</v>
       </c>
       <c r="O4" t="n">
-        <v>10.29988599876078</v>
+        <v>10.27566365271733</v>
       </c>
       <c r="P4" t="n">
-        <v>413.8285833216679</v>
+        <v>413.9044061264638</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35064,28 +35294,28 @@
         <v>0.052</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.33904334846728</v>
+        <v>-1.337027173362399</v>
       </c>
       <c r="J5" t="n">
+        <v>298</v>
+      </c>
+      <c r="K5" t="n">
         <v>296</v>
       </c>
-      <c r="K5" t="n">
-        <v>294</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.4474162491671297</v>
+        <v>0.4499439752567203</v>
       </c>
       <c r="M5" t="n">
-        <v>8.708688049534514</v>
+        <v>8.658534538744361</v>
       </c>
       <c r="N5" t="n">
-        <v>121.3790129122224</v>
+        <v>120.5846894166036</v>
       </c>
       <c r="O5" t="n">
-        <v>11.01721438986382</v>
+        <v>10.98110601973242</v>
       </c>
       <c r="P5" t="n">
-        <v>419.5333228687705</v>
+        <v>419.5122114023122</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35142,28 +35372,28 @@
         <v>0.0388</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.635549179679535</v>
+        <v>-1.62767844939935</v>
       </c>
       <c r="J6" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K6" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5097377625609727</v>
+        <v>0.5101787788033225</v>
       </c>
       <c r="M6" t="n">
-        <v>9.371364212065036</v>
+        <v>9.349032786573725</v>
       </c>
       <c r="N6" t="n">
-        <v>142.2670695603908</v>
+        <v>141.5965192597053</v>
       </c>
       <c r="O6" t="n">
-        <v>11.92757601360775</v>
+        <v>11.89943356885971</v>
       </c>
       <c r="P6" t="n">
-        <v>421.0192420044806</v>
+        <v>420.9374580429971</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35220,28 +35450,28 @@
         <v>0.0433</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.704108875249028</v>
+        <v>-1.694693972398292</v>
       </c>
       <c r="J7" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K7" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5480442664909713</v>
+        <v>0.5478874647996375</v>
       </c>
       <c r="M7" t="n">
-        <v>9.371291169143293</v>
+        <v>9.362441590930432</v>
       </c>
       <c r="N7" t="n">
-        <v>132.5635409631339</v>
+        <v>132.0602358974887</v>
       </c>
       <c r="O7" t="n">
-        <v>11.51362414546931</v>
+        <v>11.491746425043</v>
       </c>
       <c r="P7" t="n">
-        <v>417.1167563936157</v>
+        <v>417.0188754165023</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35298,28 +35528,28 @@
         <v>0.036</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.932055598010097</v>
+        <v>-1.925573674885406</v>
       </c>
       <c r="J8" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K8" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5797737557831384</v>
+        <v>0.5810581455027475</v>
       </c>
       <c r="M8" t="n">
-        <v>9.513383814558022</v>
+        <v>9.47936402796222</v>
       </c>
       <c r="N8" t="n">
-        <v>149.7659262116238</v>
+        <v>148.9665473371606</v>
       </c>
       <c r="O8" t="n">
-        <v>12.23788896058564</v>
+        <v>12.20518526435222</v>
       </c>
       <c r="P8" t="n">
-        <v>426.8050628132368</v>
+        <v>426.7376814223102</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35376,28 +35606,28 @@
         <v>0.0309</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.036492902600703</v>
+        <v>-2.026090084305716</v>
       </c>
       <c r="J9" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K9" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5376733827795672</v>
+        <v>0.537830508699122</v>
       </c>
       <c r="M9" t="n">
-        <v>10.5020077759846</v>
+        <v>10.5014123293297</v>
       </c>
       <c r="N9" t="n">
-        <v>197.73791095498</v>
+        <v>196.9035101714875</v>
       </c>
       <c r="O9" t="n">
-        <v>14.06193126689858</v>
+        <v>14.03223111880244</v>
       </c>
       <c r="P9" t="n">
-        <v>429.3656359516816</v>
+        <v>429.2576352987922</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35454,28 +35684,28 @@
         <v>0.0323</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.560449716630016</v>
+        <v>-1.556013679328103</v>
       </c>
       <c r="J10" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K10" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3833356500381957</v>
+        <v>0.3850406835557419</v>
       </c>
       <c r="M10" t="n">
-        <v>11.06973066222113</v>
+        <v>11.01911927564252</v>
       </c>
       <c r="N10" t="n">
-        <v>213.2380724559276</v>
+        <v>211.9176807878135</v>
       </c>
       <c r="O10" t="n">
-        <v>14.60267346946879</v>
+        <v>14.55739265073981</v>
       </c>
       <c r="P10" t="n">
-        <v>418.8190203916391</v>
+        <v>418.7723329987091</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35532,28 +35762,28 @@
         <v>0.0357</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.691245318476825</v>
+        <v>-1.678288196774691</v>
       </c>
       <c r="J11" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K11" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3976304683742553</v>
+        <v>0.3964309680734376</v>
       </c>
       <c r="M11" t="n">
-        <v>11.80543531279596</v>
+        <v>11.79930559045932</v>
       </c>
       <c r="N11" t="n">
-        <v>239.6029126750746</v>
+        <v>238.7220856874027</v>
       </c>
       <c r="O11" t="n">
-        <v>15.4791121410459</v>
+        <v>15.45063382801504</v>
       </c>
       <c r="P11" t="n">
-        <v>420.2828278517343</v>
+        <v>420.1481838440867</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35610,28 +35840,28 @@
         <v>0.0353</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.429571924027345</v>
+        <v>-1.42076530508668</v>
       </c>
       <c r="J12" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K12" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3176189368232692</v>
+        <v>0.3175253637799105</v>
       </c>
       <c r="M12" t="n">
-        <v>11.31262574542642</v>
+        <v>11.28585333878653</v>
       </c>
       <c r="N12" t="n">
-        <v>242.7885130640067</v>
+        <v>241.5199019361858</v>
       </c>
       <c r="O12" t="n">
-        <v>15.58167234490594</v>
+        <v>15.54091058902875</v>
       </c>
       <c r="P12" t="n">
-        <v>422.4626795933019</v>
+        <v>422.3711719847601</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35688,28 +35918,28 @@
         <v>0.0347</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.548229336554017</v>
+        <v>-1.539791521233971</v>
       </c>
       <c r="J13" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K13" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3160347327923225</v>
+        <v>0.3163108553581646</v>
       </c>
       <c r="M13" t="n">
-        <v>12.50682163333574</v>
+        <v>12.47303080233658</v>
       </c>
       <c r="N13" t="n">
-        <v>286.8569353035097</v>
+        <v>285.2781960105614</v>
       </c>
       <c r="O13" t="n">
-        <v>16.93685139875501</v>
+        <v>16.89018046116031</v>
       </c>
       <c r="P13" t="n">
-        <v>419.5107268172567</v>
+        <v>419.4230544281161</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35766,28 +35996,28 @@
         <v>0.0368</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.517557113075617</v>
+        <v>-1.513866303504886</v>
       </c>
       <c r="J14" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K14" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3270458438144533</v>
+        <v>0.3288553985581003</v>
       </c>
       <c r="M14" t="n">
-        <v>12.26848072999679</v>
+        <v>12.20686851848687</v>
       </c>
       <c r="N14" t="n">
-        <v>262.7608841826472</v>
+        <v>261.0756012379139</v>
       </c>
       <c r="O14" t="n">
-        <v>16.20990080730438</v>
+        <v>16.15783405156501</v>
       </c>
       <c r="P14" t="n">
-        <v>418.011362737547</v>
+        <v>417.973052788638</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35844,28 +36074,28 @@
         <v>0.0379</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.294636652094199</v>
+        <v>-1.291168361179492</v>
       </c>
       <c r="J15" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K15" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2846449891420635</v>
+        <v>0.2862038978039074</v>
       </c>
       <c r="M15" t="n">
-        <v>11.50813708258401</v>
+        <v>11.44537658954673</v>
       </c>
       <c r="N15" t="n">
-        <v>233.5649424124794</v>
+        <v>232.0836231709573</v>
       </c>
       <c r="O15" t="n">
-        <v>15.28283162285312</v>
+        <v>15.23429102948205</v>
       </c>
       <c r="P15" t="n">
-        <v>416.7140955990536</v>
+        <v>416.6780994439235</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35922,28 +36152,28 @@
         <v>0.0361</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.082510159579313</v>
+        <v>-1.080125801304655</v>
       </c>
       <c r="J16" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K16" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2495314009189734</v>
+        <v>0.2511641941959271</v>
       </c>
       <c r="M16" t="n">
-        <v>10.31316380523319</v>
+        <v>10.25406095666001</v>
       </c>
       <c r="N16" t="n">
-        <v>196.592648451279</v>
+        <v>195.3105065645811</v>
       </c>
       <c r="O16" t="n">
-        <v>14.02115004025272</v>
+        <v>13.97535353987802</v>
       </c>
       <c r="P16" t="n">
-        <v>415.7334091894635</v>
+        <v>415.7087200297285</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36000,28 +36230,28 @@
         <v>0.0331</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9127059569875673</v>
+        <v>-0.9085755531465696</v>
       </c>
       <c r="J17" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K17" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1843704428061068</v>
+        <v>0.1849371474647943</v>
       </c>
       <c r="M17" t="n">
-        <v>11.18908242163083</v>
+        <v>11.13405105501109</v>
       </c>
       <c r="N17" t="n">
-        <v>203.7787825227493</v>
+        <v>202.5299165345295</v>
       </c>
       <c r="O17" t="n">
-        <v>14.27511059581499</v>
+        <v>14.23130059181274</v>
       </c>
       <c r="P17" t="n">
-        <v>419.4887202265081</v>
+        <v>419.4458128119626</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -36078,28 +36308,28 @@
         <v>0.0316</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8303978703651002</v>
+        <v>-0.8241462114465854</v>
       </c>
       <c r="J18" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K18" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="L18" t="n">
-        <v>0.15768805305119</v>
+        <v>0.1573089873569403</v>
       </c>
       <c r="M18" t="n">
-        <v>10.94789131066259</v>
+        <v>10.9048740128388</v>
       </c>
       <c r="N18" t="n">
-        <v>201.9191906856315</v>
+        <v>200.782848931859</v>
       </c>
       <c r="O18" t="n">
-        <v>14.20982725741701</v>
+        <v>14.16978648151972</v>
       </c>
       <c r="P18" t="n">
-        <v>418.4583022469236</v>
+        <v>418.3927538211765</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -36156,28 +36386,28 @@
         <v>0.0318</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9213699339335112</v>
+        <v>-0.9060545501268845</v>
       </c>
       <c r="J19" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K19" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1812761972468161</v>
+        <v>0.1776328099666593</v>
       </c>
       <c r="M19" t="n">
-        <v>11.22256811281993</v>
+        <v>11.21449628421064</v>
       </c>
       <c r="N19" t="n">
-        <v>210.3350213776083</v>
+        <v>209.8612080256246</v>
       </c>
       <c r="O19" t="n">
-        <v>14.50293147531244</v>
+        <v>14.48658717661356</v>
       </c>
       <c r="P19" t="n">
-        <v>419.1602155921194</v>
+        <v>418.9992715835534</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -36234,28 +36464,28 @@
         <v>0.0296</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.351318745406002</v>
+        <v>-1.328014414144712</v>
       </c>
       <c r="J20" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K20" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2754795676301417</v>
+        <v>0.2695765030458693</v>
       </c>
       <c r="M20" t="n">
-        <v>12.55479674004664</v>
+        <v>12.55741445362998</v>
       </c>
       <c r="N20" t="n">
-        <v>262.3342636159453</v>
+        <v>262.7616503412939</v>
       </c>
       <c r="O20" t="n">
-        <v>16.19673620257937</v>
+        <v>16.20992443971575</v>
       </c>
       <c r="P20" t="n">
-        <v>431.5803421243156</v>
+        <v>431.3353949824984</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -36312,28 +36542,28 @@
         <v>0.0268</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5897005656194644</v>
+        <v>-0.5848698504775859</v>
       </c>
       <c r="J21" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K21" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="L21" t="n">
-        <v>0.05690724678053205</v>
+        <v>0.05672757113530058</v>
       </c>
       <c r="M21" t="n">
-        <v>14.16899095276876</v>
+        <v>14.10222597634083</v>
       </c>
       <c r="N21" t="n">
-        <v>317.8239440363989</v>
+        <v>315.7652185958062</v>
       </c>
       <c r="O21" t="n">
-        <v>17.82761745260423</v>
+        <v>17.76978386463398</v>
       </c>
       <c r="P21" t="n">
-        <v>422.6947532979042</v>
+        <v>422.6442997964956</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -36390,28 +36620,28 @@
         <v>0.0323</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.357913554988565</v>
+        <v>-1.359268162664939</v>
       </c>
       <c r="J22" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K22" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2909167777201342</v>
+        <v>0.2940967531671711</v>
       </c>
       <c r="M22" t="n">
-        <v>12.61144762649835</v>
+        <v>12.53343887731654</v>
       </c>
       <c r="N22" t="n">
-        <v>249.2105754945433</v>
+        <v>247.5399824939968</v>
       </c>
       <c r="O22" t="n">
-        <v>15.78640476785463</v>
+        <v>15.7334033983114</v>
       </c>
       <c r="P22" t="n">
-        <v>427.8166984972716</v>
+        <v>427.830764224771</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -36468,28 +36698,28 @@
         <v>0.0255</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.433449971078722</v>
+        <v>-1.444058632528668</v>
       </c>
       <c r="J23" t="n">
+        <v>298</v>
+      </c>
+      <c r="K23" t="n">
         <v>296</v>
       </c>
-      <c r="K23" t="n">
-        <v>294</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.2751412928529262</v>
+        <v>0.2804058525394945</v>
       </c>
       <c r="M23" t="n">
-        <v>13.31387730065567</v>
+        <v>13.28334680305888</v>
       </c>
       <c r="N23" t="n">
-        <v>298.2389845206401</v>
+        <v>296.7958420036418</v>
       </c>
       <c r="O23" t="n">
-        <v>17.2695971151802</v>
+        <v>17.22776369711524</v>
       </c>
       <c r="P23" t="n">
-        <v>437.1298170850948</v>
+        <v>437.2405892507585</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -36546,28 +36776,28 @@
         <v>0.031</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.421514659406402</v>
+        <v>-1.436446610945046</v>
       </c>
       <c r="J24" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K24" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="L24" t="n">
-        <v>0.198736486435045</v>
+        <v>0.2039256480544352</v>
       </c>
       <c r="M24" t="n">
-        <v>16.27163202697528</v>
+        <v>16.22422162067133</v>
       </c>
       <c r="N24" t="n">
-        <v>448.4222212684929</v>
+        <v>446.3841834460323</v>
       </c>
       <c r="O24" t="n">
-        <v>21.17598217954702</v>
+        <v>21.12780593071681</v>
       </c>
       <c r="P24" t="n">
-        <v>438.2508276893127</v>
+        <v>438.4063961936175</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -36624,28 +36854,28 @@
         <v>0.0306</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.11436212739901</v>
+        <v>-1.116710471814448</v>
       </c>
       <c r="J25" t="n">
+        <v>298</v>
+      </c>
+      <c r="K25" t="n">
         <v>296</v>
       </c>
-      <c r="K25" t="n">
-        <v>294</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.1395125661519933</v>
+        <v>0.141629282245627</v>
       </c>
       <c r="M25" t="n">
-        <v>16.35247322055137</v>
+        <v>16.26764302035291</v>
       </c>
       <c r="N25" t="n">
-        <v>424.2673551182959</v>
+        <v>421.5222038014579</v>
       </c>
       <c r="O25" t="n">
-        <v>20.59775121507918</v>
+        <v>20.53100591304425</v>
       </c>
       <c r="P25" t="n">
-        <v>430.564372165069</v>
+        <v>430.5887318254049</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -36702,28 +36932,28 @@
         <v>0.0253</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.8393325692613267</v>
+        <v>-0.8305333549657795</v>
       </c>
       <c r="J26" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K26" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="L26" t="n">
-        <v>0.08223797455210213</v>
+        <v>0.0815790898269364</v>
       </c>
       <c r="M26" t="n">
-        <v>17.06004095892983</v>
+        <v>16.99585874200562</v>
       </c>
       <c r="N26" t="n">
-        <v>434.7317565328088</v>
+        <v>432.2920102954751</v>
       </c>
       <c r="O26" t="n">
-        <v>20.85022197802241</v>
+        <v>20.79163318009134</v>
       </c>
       <c r="P26" t="n">
-        <v>428.5354120638766</v>
+        <v>428.4439981342811</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -36780,28 +37010,28 @@
         <v>0.0254</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.7710881764526191</v>
+        <v>-0.7732687759484411</v>
       </c>
       <c r="J27" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K27" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="L27" t="n">
-        <v>0.05204087031726068</v>
+        <v>0.05297393457770216</v>
       </c>
       <c r="M27" t="n">
-        <v>20.07441659252429</v>
+        <v>19.97255528929029</v>
       </c>
       <c r="N27" t="n">
-        <v>598.8922410535185</v>
+        <v>595.0600488614195</v>
       </c>
       <c r="O27" t="n">
-        <v>24.472274946427</v>
+        <v>24.39385268590059</v>
       </c>
       <c r="P27" t="n">
-        <v>417.2667303105574</v>
+        <v>417.2894277900876</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -36862,28 +37092,28 @@
         <v>0.0321</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.326105943417284</v>
+        <v>-0.2944603799251866</v>
       </c>
       <c r="J28" t="n">
+        <v>298</v>
+      </c>
+      <c r="K28" t="n">
         <v>296</v>
       </c>
-      <c r="K28" t="n">
-        <v>294</v>
-      </c>
       <c r="L28" t="n">
-        <v>0.007425573987929757</v>
+        <v>0.006109296020504251</v>
       </c>
       <c r="M28" t="n">
-        <v>22.41252066282675</v>
+        <v>22.47639022472532</v>
       </c>
       <c r="N28" t="n">
-        <v>791.0540899992643</v>
+        <v>790.187236288573</v>
       </c>
       <c r="O28" t="n">
-        <v>28.12568381389623</v>
+        <v>28.11026923187633</v>
       </c>
       <c r="P28" t="n">
-        <v>405.6207117195081</v>
+        <v>405.2927334280653</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -36944,28 +37174,28 @@
         <v>0.0261</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.732846733416324</v>
+        <v>-0.6576114994724558</v>
       </c>
       <c r="J29" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K29" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="L29" t="n">
-        <v>0.0252083023497468</v>
+        <v>0.02025490666979912</v>
       </c>
       <c r="M29" t="n">
-        <v>27.27710122354636</v>
+        <v>27.58955688920889</v>
       </c>
       <c r="N29" t="n">
-        <v>1145.381223051519</v>
+        <v>1161.267322728516</v>
       </c>
       <c r="O29" t="n">
-        <v>33.84348124900155</v>
+        <v>34.07737259133274</v>
       </c>
       <c r="P29" t="n">
-        <v>424.1085751970475</v>
+        <v>423.3224918117478</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -37026,28 +37256,28 @@
         <v>0.0271</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.5253616838443134</v>
+        <v>-0.4282046129765384</v>
       </c>
       <c r="J30" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K30" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L30" t="n">
-        <v>0.01253418761015301</v>
+        <v>0.008206404890401919</v>
       </c>
       <c r="M30" t="n">
-        <v>27.42938348032344</v>
+        <v>27.79257431052265</v>
       </c>
       <c r="N30" t="n">
-        <v>1202.580370246348</v>
+        <v>1233.621608737899</v>
       </c>
       <c r="O30" t="n">
-        <v>34.67824058752618</v>
+        <v>35.12294988661828</v>
       </c>
       <c r="P30" t="n">
-        <v>432.9860789293934</v>
+        <v>431.97196806266</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -37108,28 +37338,28 @@
         <v>0.0304</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5044829547910092</v>
+        <v>-0.4029349737553397</v>
       </c>
       <c r="J31" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K31" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="L31" t="n">
-        <v>0.01076582891545397</v>
+        <v>0.006763777900866241</v>
       </c>
       <c r="M31" t="n">
-        <v>28.86110122132183</v>
+        <v>29.30467599370269</v>
       </c>
       <c r="N31" t="n">
-        <v>1289.258872822624</v>
+        <v>1323.075049099589</v>
       </c>
       <c r="O31" t="n">
-        <v>35.90625116637247</v>
+        <v>36.37409860188414</v>
       </c>
       <c r="P31" t="n">
-        <v>444.4382182738064</v>
+        <v>443.3769095713959</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -37190,28 +37420,28 @@
         <v>0.0209</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.02462828521992375</v>
+        <v>0.08786387049823763</v>
       </c>
       <c r="J32" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K32" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="L32" t="n">
-        <v>2.767613193799257e-05</v>
+        <v>0.0003422654742368803</v>
       </c>
       <c r="M32" t="n">
-        <v>28.04666530918842</v>
+        <v>28.55817367235709</v>
       </c>
       <c r="N32" t="n">
-        <v>1202.358529134543</v>
+        <v>1245.165211750417</v>
       </c>
       <c r="O32" t="n">
-        <v>34.67504187646416</v>
+        <v>35.28689858503319</v>
       </c>
       <c r="P32" t="n">
-        <v>442.781512374698</v>
+        <v>441.5999655466491</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -37253,7 +37483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG297"/>
+  <dimension ref="A1:AG299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86626,12 +86856,346 @@
       </c>
       <c r="AF297" t="inlineStr">
         <is>
-          <t>-37.80414011896538,174.83947551510977</t>
+          <t>-37.804042896724546,174.8393758266927</t>
         </is>
       </c>
       <c r="AG297" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>-37.821390010171456,174.82441337719285</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>-37.82106314193832,174.8252399696722</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>-37.820573307494165,174.82586987247421</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>-37.82004231245269,174.82641010446898</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>-37.8194746720904,174.82689344414518</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>-37.81891397877055,174.8274486706023</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>-37.81833417116453,174.82794036732219</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>-37.81771985592208,174.82833717286601</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>-37.81710149135109,174.82875393865666</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>-37.81643898908248,174.8290962359237</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>-37.81580919240045,174.8294646075118</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>-37.815179777604655,174.82983618000154</t>
+        </is>
+      </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>-37.81453995251731,174.83025451865345</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>-37.81387479134722,174.8305760936315</t>
+        </is>
+      </c>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>-37.813217300619215,174.8309133955012</t>
+        </is>
+      </c>
+      <c r="Q298" t="inlineStr">
+        <is>
+          <t>-37.8125342409348,174.8311741306091</t>
+        </is>
+      </c>
+      <c r="R298" t="inlineStr">
+        <is>
+          <t>-37.81187473434829,174.8315046613049</t>
+        </is>
+      </c>
+      <c r="S298" t="inlineStr">
+        <is>
+          <t>-37.811209026692396,174.831853325309</t>
+        </is>
+      </c>
+      <c r="T298" t="inlineStr">
+        <is>
+          <t>-37.81053116186057,174.8321916968596</t>
+        </is>
+      </c>
+      <c r="U298" t="inlineStr">
+        <is>
+          <t>-37.80991417549134,174.83265416985674</t>
+        </is>
+      </c>
+      <c r="V298" t="inlineStr">
+        <is>
+          <t>-37.80934820247019,174.8332950898363</t>
+        </is>
+      </c>
+      <c r="W298" t="inlineStr">
+        <is>
+          <t>-37.80874437736877,174.83383589112364</t>
+        </is>
+      </c>
+      <c r="X298" t="inlineStr">
+        <is>
+          <t>-37.80820078821832,174.83444192456017</t>
+        </is>
+      </c>
+      <c r="Y298" t="inlineStr">
+        <is>
+          <t>-37.807606984258825,174.83499276185847</t>
+        </is>
+      </c>
+      <c r="Z298" t="inlineStr">
+        <is>
+          <t>-37.80701720331701,174.8355467398509</t>
+        </is>
+      </c>
+      <c r="AA298" t="inlineStr">
+        <is>
+          <t>-37.80662621597426,174.83638429943198</t>
+        </is>
+      </c>
+      <c r="AB298" t="inlineStr">
+        <is>
+          <t>-37.8060048877784,174.83705594627594</t>
+        </is>
+      </c>
+      <c r="AC298" t="inlineStr">
+        <is>
+          <t>-37.80535206645708,174.8377090890588</t>
+        </is>
+      </c>
+      <c r="AD298" t="inlineStr">
+        <is>
+          <t>-37.80483898754634,174.8383260602356</t>
+        </is>
+      </c>
+      <c r="AE298" t="inlineStr">
+        <is>
+          <t>-37.80447691011115,174.83885100705433</t>
+        </is>
+      </c>
+      <c r="AF298" t="inlineStr">
+        <is>
+          <t>-37.804027310404116,174.83935984503708</t>
+        </is>
+      </c>
+      <c r="AG298" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:06:24+00:00</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>-37.82141668459266,174.82444308059354</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>-37.82107729109087,174.82525631581538</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>-37.82058113538683,174.82587992237052</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>-37.8200553333265,174.8264314408835</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>-37.819495363873294,174.82693325125132</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>-37.818932821956984,174.82748375195226</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>-37.8183559686247,174.82798520664855</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>-37.817742003971965,174.8283922939199</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>-37.81712132343661,174.82880782471474</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>-37.8164576132129,174.829143292091</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>-37.81582747563963,174.82951626148187</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>-37.81519828736677,174.8298959595071</t>
+        </is>
+      </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>-37.81455449315193,174.83029720272785</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>-37.81389284784766,174.8306281208388</t>
+        </is>
+      </c>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>-37.81323169234429,174.8309550463148</t>
+        </is>
+      </c>
+      <c r="Q299" t="inlineStr">
+        <is>
+          <t>-37.812553488422154,174.83123033400796</t>
+        </is>
+      </c>
+      <c r="R299" t="inlineStr">
+        <is>
+          <t>-37.81189807049624,174.8315731125987</t>
+        </is>
+      </c>
+      <c r="S299" t="inlineStr">
+        <is>
+          <t>-37.811209026692396,174.831853325309</t>
+        </is>
+      </c>
+      <c r="T299" t="inlineStr">
+        <is>
+          <t>-37.81053116186057,174.8321916968596</t>
+        </is>
+      </c>
+      <c r="U299" t="inlineStr">
+        <is>
+          <t>-37.80991417549134,174.83265416985674</t>
+        </is>
+      </c>
+      <c r="V299" t="inlineStr">
+        <is>
+          <t>-37.80934820247019,174.8332950898363</t>
+        </is>
+      </c>
+      <c r="W299" t="inlineStr">
+        <is>
+          <t>-37.80878981837442,174.83390816547413</t>
+        </is>
+      </c>
+      <c r="X299" t="inlineStr">
+        <is>
+          <t>-37.808246697290365,174.83450869535056</t>
+        </is>
+      </c>
+      <c r="Y299" t="inlineStr">
+        <is>
+          <t>-37.80765558364964,174.83505500957668</t>
+        </is>
+      </c>
+      <c r="Z299" t="inlineStr">
+        <is>
+          <t>-37.807080741409166,174.8356228760676</t>
+        </is>
+      </c>
+      <c r="AA299" t="inlineStr">
+        <is>
+          <t>-37.80669766491252,174.83645367606775</t>
+        </is>
+      </c>
+      <c r="AB299" t="inlineStr">
+        <is>
+          <t>-37.80611329626382,174.83712987815025</t>
+        </is>
+      </c>
+      <c r="AC299" t="inlineStr">
+        <is>
+          <t>-37.80546263207399,174.83777488344634</t>
+        </is>
+      </c>
+      <c r="AD299" t="inlineStr">
+        <is>
+          <t>-37.80491617888701,174.838376747173</t>
+        </is>
+      </c>
+      <c r="AE299" t="inlineStr">
+        <is>
+          <t>-37.804522816825944,174.8388907277769</t>
+        </is>
+      </c>
+      <c r="AF299" t="inlineStr">
+        <is>
+          <t>-37.80405827336118,174.83939159335506</t>
+        </is>
+      </c>
+      <c r="AG299" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0228/nzd0228.xlsx
+++ b/data/nzd0228/nzd0228.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG299"/>
+  <dimension ref="A1:AG301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31731,10 +31731,10 @@
         <v>398.34</v>
       </c>
       <c r="S299" t="n">
-        <v>407.03</v>
+        <v>400.44</v>
       </c>
       <c r="T299" t="n">
-        <v>414.42</v>
+        <v>407.53</v>
       </c>
       <c r="U299" t="n">
         <v>411.06</v>
@@ -31773,6 +31773,216 @@
         <v>521.11</v>
       </c>
       <c r="AG299" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:06:17+00:00</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>392.34</v>
+      </c>
+      <c r="C300" t="n">
+        <v>377.29</v>
+      </c>
+      <c r="D300" t="n">
+        <v>381.4</v>
+      </c>
+      <c r="E300" t="n">
+        <v>385.87</v>
+      </c>
+      <c r="F300" t="n">
+        <v>382.65</v>
+      </c>
+      <c r="G300" t="n">
+        <v>376.65</v>
+      </c>
+      <c r="H300" t="n">
+        <v>376.96</v>
+      </c>
+      <c r="I300" t="n">
+        <v>379.22</v>
+      </c>
+      <c r="J300" t="n">
+        <v>378.18</v>
+      </c>
+      <c r="K300" t="n">
+        <v>383.18</v>
+      </c>
+      <c r="L300" t="n">
+        <v>388.92</v>
+      </c>
+      <c r="M300" t="n">
+        <v>381.31</v>
+      </c>
+      <c r="N300" t="n">
+        <v>378.24</v>
+      </c>
+      <c r="O300" t="n">
+        <v>381.81</v>
+      </c>
+      <c r="P300" t="n">
+        <v>386.38</v>
+      </c>
+      <c r="Q300" t="n">
+        <v>395.59</v>
+      </c>
+      <c r="R300" t="n">
+        <v>399.04</v>
+      </c>
+      <c r="S300" t="n">
+        <v>401.16</v>
+      </c>
+      <c r="T300" t="n">
+        <v>408.15</v>
+      </c>
+      <c r="U300" t="n">
+        <v>412.41</v>
+      </c>
+      <c r="V300" t="n">
+        <v>392.51</v>
+      </c>
+      <c r="W300" t="n">
+        <v>386.73</v>
+      </c>
+      <c r="X300" t="n">
+        <v>384.59</v>
+      </c>
+      <c r="Y300" t="n">
+        <v>393.12</v>
+      </c>
+      <c r="Z300" t="n">
+        <v>404.76</v>
+      </c>
+      <c r="AA300" t="n">
+        <v>386.04</v>
+      </c>
+      <c r="AB300" t="n">
+        <v>407.75</v>
+      </c>
+      <c r="AC300" t="n">
+        <v>450.15</v>
+      </c>
+      <c r="AD300" t="n">
+        <v>484.33</v>
+      </c>
+      <c r="AE300" t="n">
+        <v>505.6</v>
+      </c>
+      <c r="AF300" t="n">
+        <v>520.79</v>
+      </c>
+      <c r="AG300" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:25+00:00</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>392.34</v>
+      </c>
+      <c r="C301" t="n">
+        <v>377.29</v>
+      </c>
+      <c r="D301" t="n">
+        <v>381.4</v>
+      </c>
+      <c r="E301" t="n">
+        <v>385.87</v>
+      </c>
+      <c r="F301" t="n">
+        <v>382.65</v>
+      </c>
+      <c r="G301" t="n">
+        <v>376.65</v>
+      </c>
+      <c r="H301" t="n">
+        <v>376.96</v>
+      </c>
+      <c r="I301" t="n">
+        <v>379.22</v>
+      </c>
+      <c r="J301" t="n">
+        <v>378.18</v>
+      </c>
+      <c r="K301" t="n">
+        <v>383.18</v>
+      </c>
+      <c r="L301" t="n">
+        <v>388.92</v>
+      </c>
+      <c r="M301" t="n">
+        <v>381.31</v>
+      </c>
+      <c r="N301" t="n">
+        <v>378.24</v>
+      </c>
+      <c r="O301" t="n">
+        <v>381.81</v>
+      </c>
+      <c r="P301" t="n">
+        <v>386.38</v>
+      </c>
+      <c r="Q301" t="n">
+        <v>396.25</v>
+      </c>
+      <c r="R301" t="n">
+        <v>399.89</v>
+      </c>
+      <c r="S301" t="n">
+        <v>401.16</v>
+      </c>
+      <c r="T301" t="n">
+        <v>408.15</v>
+      </c>
+      <c r="U301" t="n">
+        <v>412.41</v>
+      </c>
+      <c r="V301" t="n">
+        <v>392.51</v>
+      </c>
+      <c r="W301" t="n">
+        <v>386.73</v>
+      </c>
+      <c r="X301" t="n">
+        <v>384.59</v>
+      </c>
+      <c r="Y301" t="n">
+        <v>393.12</v>
+      </c>
+      <c r="Z301" t="n">
+        <v>404.76</v>
+      </c>
+      <c r="AA301" t="n">
+        <v>386.04</v>
+      </c>
+      <c r="AB301" t="n">
+        <v>407.75</v>
+      </c>
+      <c r="AC301" t="n">
+        <v>450.15</v>
+      </c>
+      <c r="AD301" t="n">
+        <v>484.33</v>
+      </c>
+      <c r="AE301" t="n">
+        <v>505.6</v>
+      </c>
+      <c r="AF301" t="n">
+        <v>522.4</v>
+      </c>
+      <c r="AG301" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -31789,7 +31999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B310"/>
+  <dimension ref="A1:B312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34892,6 +35102,26 @@
       </c>
       <c r="B310" t="n">
         <v>0.28</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>0.84</v>
       </c>
     </row>
   </sheetData>
@@ -35060,28 +35290,28 @@
         <v>0.0389</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4412856762858344</v>
+        <v>-0.4475944489565458</v>
       </c>
       <c r="J2" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K2" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1505824832746762</v>
+        <v>0.1556201622907137</v>
       </c>
       <c r="M2" t="n">
-        <v>5.674797436039861</v>
+        <v>5.664472440472491</v>
       </c>
       <c r="N2" t="n">
-        <v>60.59508486106192</v>
+        <v>60.35582106603387</v>
       </c>
       <c r="O2" t="n">
-        <v>7.78428447971051</v>
+        <v>7.768900891762867</v>
       </c>
       <c r="P2" t="n">
-        <v>408.9500283603307</v>
+        <v>409.0161871741466</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35138,28 +35368,28 @@
         <v>0.0413</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9289064068381815</v>
+        <v>-0.9358259590802642</v>
       </c>
       <c r="J3" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K3" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L3" t="n">
-        <v>0.321241913616639</v>
+        <v>0.3269517274629958</v>
       </c>
       <c r="M3" t="n">
-        <v>7.796706450916592</v>
+        <v>7.772457101595365</v>
       </c>
       <c r="N3" t="n">
-        <v>100.5721436944666</v>
+        <v>100.0991850436171</v>
       </c>
       <c r="O3" t="n">
-        <v>10.02856638281198</v>
+        <v>10.00495802308121</v>
       </c>
       <c r="P3" t="n">
-        <v>407.1778070509299</v>
+        <v>407.2503709513888</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35216,28 +35446,28 @@
         <v>0.0432</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.067452442010383</v>
+        <v>-1.073107450213859</v>
       </c>
       <c r="J4" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K4" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3731545630570691</v>
+        <v>0.3784362569844439</v>
       </c>
       <c r="M4" t="n">
-        <v>8.596286642204349</v>
+        <v>8.570905814113891</v>
       </c>
       <c r="N4" t="n">
-        <v>105.589263503776</v>
+        <v>105.0164040330302</v>
       </c>
       <c r="O4" t="n">
-        <v>10.27566365271733</v>
+        <v>10.24775116955082</v>
       </c>
       <c r="P4" t="n">
-        <v>413.9044061264638</v>
+        <v>413.9637089936948</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35294,28 +35524,28 @@
         <v>0.052</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.337027173362399</v>
+        <v>-1.33523244876765</v>
       </c>
       <c r="J5" t="n">
+        <v>300</v>
+      </c>
+      <c r="K5" t="n">
         <v>298</v>
       </c>
-      <c r="K5" t="n">
-        <v>296</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.4499439752567203</v>
+        <v>0.4525196677818244</v>
       </c>
       <c r="M5" t="n">
-        <v>8.658534538744361</v>
+        <v>8.608072708024874</v>
       </c>
       <c r="N5" t="n">
-        <v>120.5846894166036</v>
+        <v>119.7888591856796</v>
       </c>
       <c r="O5" t="n">
-        <v>10.98110601973242</v>
+        <v>10.94480969161545</v>
       </c>
       <c r="P5" t="n">
-        <v>419.5122114023122</v>
+        <v>419.4933713876549</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35372,28 +35602,28 @@
         <v>0.0388</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.62767844939935</v>
+        <v>-1.622198189771356</v>
       </c>
       <c r="J6" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K6" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5101787788033225</v>
+        <v>0.5115608649951644</v>
       </c>
       <c r="M6" t="n">
-        <v>9.349032786573725</v>
+        <v>9.315530030965261</v>
       </c>
       <c r="N6" t="n">
-        <v>141.5965192597053</v>
+        <v>140.7794012934289</v>
       </c>
       <c r="O6" t="n">
-        <v>11.89943356885971</v>
+        <v>11.86504956978389</v>
       </c>
       <c r="P6" t="n">
-        <v>420.9374580429971</v>
+        <v>420.8803818106493</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35450,28 +35680,28 @@
         <v>0.0433</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.694693972398292</v>
+        <v>-1.689612740515462</v>
       </c>
       <c r="J7" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K7" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5478874647996375</v>
+        <v>0.5494517762013194</v>
       </c>
       <c r="M7" t="n">
-        <v>9.362441590930432</v>
+        <v>9.328964708546449</v>
       </c>
       <c r="N7" t="n">
-        <v>132.0602358974887</v>
+        <v>131.2862336159641</v>
       </c>
       <c r="O7" t="n">
-        <v>11.491746425043</v>
+        <v>11.45802049291081</v>
       </c>
       <c r="P7" t="n">
-        <v>417.0188754165023</v>
+        <v>416.9659288927465</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35528,28 +35758,28 @@
         <v>0.036</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.925573674885406</v>
+        <v>-1.924673795494594</v>
       </c>
       <c r="J8" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K8" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5810581455027475</v>
+        <v>0.5840245024243638</v>
       </c>
       <c r="M8" t="n">
-        <v>9.47936402796222</v>
+        <v>9.420100230025596</v>
       </c>
       <c r="N8" t="n">
-        <v>148.9665473371606</v>
+        <v>147.9735477565464</v>
       </c>
       <c r="O8" t="n">
-        <v>12.20518526435222</v>
+        <v>12.16443783150485</v>
       </c>
       <c r="P8" t="n">
-        <v>426.7376814223102</v>
+        <v>426.7283045385707</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35606,28 +35836,28 @@
         <v>0.0309</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.026090084305716</v>
+        <v>-2.02222715110317</v>
       </c>
       <c r="J9" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K9" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L9" t="n">
-        <v>0.537830508699122</v>
+        <v>0.5400713475924233</v>
       </c>
       <c r="M9" t="n">
-        <v>10.5014123293297</v>
+        <v>10.45693060003938</v>
       </c>
       <c r="N9" t="n">
-        <v>196.9035101714875</v>
+        <v>195.649724110092</v>
       </c>
       <c r="O9" t="n">
-        <v>14.03223111880244</v>
+        <v>13.98748455263104</v>
       </c>
       <c r="P9" t="n">
-        <v>429.2576352987922</v>
+        <v>429.2174378122832</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35684,28 +35914,28 @@
         <v>0.0323</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.556013679328103</v>
+        <v>-1.555737899392523</v>
       </c>
       <c r="J10" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K10" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3850406835557419</v>
+        <v>0.3880969809971966</v>
       </c>
       <c r="M10" t="n">
-        <v>11.01911927564252</v>
+        <v>10.94641793282073</v>
       </c>
       <c r="N10" t="n">
-        <v>211.9176807878135</v>
+        <v>210.4909422504427</v>
       </c>
       <c r="O10" t="n">
-        <v>14.55739265073981</v>
+        <v>14.50830597452517</v>
       </c>
       <c r="P10" t="n">
-        <v>418.7723329987091</v>
+        <v>418.7694231278981</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35762,28 +35992,28 @@
         <v>0.0357</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.678288196774691</v>
+        <v>-1.669517505593832</v>
       </c>
       <c r="J11" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K11" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3964309680734376</v>
+        <v>0.3967490133896112</v>
       </c>
       <c r="M11" t="n">
-        <v>11.79930559045932</v>
+        <v>11.77007956470472</v>
       </c>
       <c r="N11" t="n">
-        <v>238.7220856874027</v>
+        <v>237.4555301362353</v>
       </c>
       <c r="O11" t="n">
-        <v>15.45063382801504</v>
+        <v>15.40959214697895</v>
       </c>
       <c r="P11" t="n">
-        <v>420.1481838440867</v>
+        <v>420.0568382412748</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35840,28 +36070,28 @@
         <v>0.0353</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.42076530508668</v>
+        <v>-1.416016334281562</v>
       </c>
       <c r="J12" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K12" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3175253637799105</v>
+        <v>0.3188453339183905</v>
       </c>
       <c r="M12" t="n">
-        <v>11.28585333878653</v>
+        <v>11.23691222679082</v>
       </c>
       <c r="N12" t="n">
-        <v>241.5199019361858</v>
+        <v>240.0050307769501</v>
       </c>
       <c r="O12" t="n">
-        <v>15.54091058902875</v>
+        <v>15.49209575160669</v>
       </c>
       <c r="P12" t="n">
-        <v>422.3711719847601</v>
+        <v>422.321712035087</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35918,28 +36148,28 @@
         <v>0.0347</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.539791521233971</v>
+        <v>-1.536959908290223</v>
       </c>
       <c r="J13" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K13" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3163108553581646</v>
+        <v>0.3183421649370326</v>
       </c>
       <c r="M13" t="n">
-        <v>12.47303080233658</v>
+        <v>12.40662358410332</v>
       </c>
       <c r="N13" t="n">
-        <v>285.2781960105614</v>
+        <v>283.4102101982605</v>
       </c>
       <c r="O13" t="n">
-        <v>16.89018046116031</v>
+        <v>16.83479165889084</v>
       </c>
       <c r="P13" t="n">
-        <v>419.4230544281161</v>
+        <v>419.3935634729145</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35996,28 +36226,28 @@
         <v>0.0368</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.513866303504886</v>
+        <v>-1.51390093727503</v>
       </c>
       <c r="J14" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K14" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3288553985581003</v>
+        <v>0.3317762533278249</v>
       </c>
       <c r="M14" t="n">
-        <v>12.20686851848687</v>
+        <v>12.12538770621442</v>
       </c>
       <c r="N14" t="n">
-        <v>261.0756012379139</v>
+        <v>259.3292830786071</v>
       </c>
       <c r="O14" t="n">
-        <v>16.15783405156501</v>
+        <v>16.10370401735598</v>
       </c>
       <c r="P14" t="n">
-        <v>417.973052788638</v>
+        <v>417.9734130681999</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36074,28 +36304,28 @@
         <v>0.0379</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.291168361179492</v>
+        <v>-1.292409572217632</v>
       </c>
       <c r="J15" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K15" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2862038978039074</v>
+        <v>0.2892887237237175</v>
       </c>
       <c r="M15" t="n">
-        <v>11.44537658954673</v>
+        <v>11.37669909508456</v>
       </c>
       <c r="N15" t="n">
-        <v>232.0836231709573</v>
+        <v>230.5377602813144</v>
       </c>
       <c r="O15" t="n">
-        <v>15.23429102948205</v>
+        <v>15.18346996840032</v>
       </c>
       <c r="P15" t="n">
-        <v>416.6780994439235</v>
+        <v>416.6910152736852</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36152,28 +36382,28 @@
         <v>0.0361</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.080125801304655</v>
+        <v>-1.081364533728188</v>
       </c>
       <c r="J16" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K16" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2511641941959271</v>
+        <v>0.2540687042811655</v>
       </c>
       <c r="M16" t="n">
-        <v>10.25406095666001</v>
+        <v>10.19292205843437</v>
       </c>
       <c r="N16" t="n">
-        <v>195.3105065645811</v>
+        <v>194.0018483520529</v>
       </c>
       <c r="O16" t="n">
-        <v>13.97535353987802</v>
+        <v>13.9284546289979</v>
       </c>
       <c r="P16" t="n">
-        <v>415.7087200297285</v>
+        <v>415.7215816951119</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36230,28 +36460,28 @@
         <v>0.0331</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9085755531465696</v>
+        <v>-0.9082001143384971</v>
       </c>
       <c r="J17" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K17" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1849371474647943</v>
+        <v>0.1868051081751552</v>
       </c>
       <c r="M17" t="n">
-        <v>11.13405105501109</v>
+        <v>11.06192495136071</v>
       </c>
       <c r="N17" t="n">
-        <v>202.5299165345295</v>
+        <v>201.1810855362664</v>
       </c>
       <c r="O17" t="n">
-        <v>14.23130059181274</v>
+        <v>14.18383183544794</v>
       </c>
       <c r="P17" t="n">
-        <v>419.4458128119626</v>
+        <v>419.441900290971</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -36308,28 +36538,28 @@
         <v>0.0316</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8241462114465854</v>
+        <v>-0.8207673382361164</v>
       </c>
       <c r="J18" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K18" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1573089873569403</v>
+        <v>0.1579342098599493</v>
       </c>
       <c r="M18" t="n">
-        <v>10.9048740128388</v>
+        <v>10.84819449375874</v>
       </c>
       <c r="N18" t="n">
-        <v>200.782848931859</v>
+        <v>199.47984996245</v>
       </c>
       <c r="O18" t="n">
-        <v>14.16978648151972</v>
+        <v>14.12373357021613</v>
       </c>
       <c r="P18" t="n">
-        <v>418.3927538211765</v>
+        <v>418.3572352101537</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -36386,28 +36616,28 @@
         <v>0.0318</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9060545501268845</v>
+        <v>-0.902729304896086</v>
       </c>
       <c r="J19" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K19" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1776328099666593</v>
+        <v>0.1785774130514223</v>
       </c>
       <c r="M19" t="n">
-        <v>11.21449628421064</v>
+        <v>11.15311967497474</v>
       </c>
       <c r="N19" t="n">
-        <v>209.8612080256246</v>
+        <v>208.2975590675052</v>
       </c>
       <c r="O19" t="n">
-        <v>14.48658717661356</v>
+        <v>14.43251741961551</v>
       </c>
       <c r="P19" t="n">
-        <v>418.9992715835534</v>
+        <v>418.9641814593315</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -36464,28 +36694,28 @@
         <v>0.0296</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.328014414144712</v>
+        <v>-1.317669299020815</v>
       </c>
       <c r="J20" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K20" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2695765030458693</v>
+        <v>0.2689187584729495</v>
       </c>
       <c r="M20" t="n">
-        <v>12.55741445362998</v>
+        <v>12.51149727456923</v>
       </c>
       <c r="N20" t="n">
-        <v>262.7616503412939</v>
+        <v>261.228050056218</v>
       </c>
       <c r="O20" t="n">
-        <v>16.20992443971575</v>
+        <v>16.16255085239387</v>
       </c>
       <c r="P20" t="n">
-        <v>431.3353949824984</v>
+        <v>431.2263552593288</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -36542,28 +36772,28 @@
         <v>0.0268</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5848698504775859</v>
+        <v>-0.5784824870452816</v>
       </c>
       <c r="J21" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K21" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L21" t="n">
-        <v>0.05672757113530058</v>
+        <v>0.05622915605416945</v>
       </c>
       <c r="M21" t="n">
-        <v>14.10222597634083</v>
+        <v>14.04558304069598</v>
       </c>
       <c r="N21" t="n">
-        <v>315.7652185958062</v>
+        <v>313.8109575866095</v>
       </c>
       <c r="O21" t="n">
-        <v>17.76978386463398</v>
+        <v>17.71471020329177</v>
       </c>
       <c r="P21" t="n">
-        <v>422.6442997964956</v>
+        <v>422.577445327391</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -36620,28 +36850,28 @@
         <v>0.0323</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.359268162664939</v>
+        <v>-1.358856641739379</v>
       </c>
       <c r="J22" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K22" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2940967531671711</v>
+        <v>0.2967088903573365</v>
       </c>
       <c r="M22" t="n">
-        <v>12.53343887731654</v>
+        <v>12.45186538950341</v>
       </c>
       <c r="N22" t="n">
-        <v>247.5399824939968</v>
+        <v>245.8849163582426</v>
       </c>
       <c r="O22" t="n">
-        <v>15.7334033983114</v>
+        <v>15.68071797967946</v>
       </c>
       <c r="P22" t="n">
-        <v>427.830764224771</v>
+        <v>427.8264818711048</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -36698,28 +36928,28 @@
         <v>0.0255</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.444058632528668</v>
+        <v>-1.459858127688876</v>
       </c>
       <c r="J23" t="n">
+        <v>300</v>
+      </c>
+      <c r="K23" t="n">
         <v>298</v>
       </c>
-      <c r="K23" t="n">
-        <v>296</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.2804058525394945</v>
+        <v>0.286782363411211</v>
       </c>
       <c r="M23" t="n">
-        <v>13.28334680305888</v>
+        <v>13.28358279606779</v>
       </c>
       <c r="N23" t="n">
-        <v>296.7958420036418</v>
+        <v>295.85422110785</v>
       </c>
       <c r="O23" t="n">
-        <v>17.22776369711524</v>
+        <v>17.20041339932997</v>
       </c>
       <c r="P23" t="n">
-        <v>437.2405892507585</v>
+        <v>437.4058711179951</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -36776,28 +37006,28 @@
         <v>0.031</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.436446610945046</v>
+        <v>-1.456813416220334</v>
       </c>
       <c r="J24" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K24" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2039256480544352</v>
+        <v>0.2101070291272303</v>
       </c>
       <c r="M24" t="n">
-        <v>16.22422162067133</v>
+        <v>16.20049566697962</v>
       </c>
       <c r="N24" t="n">
-        <v>446.3841834460323</v>
+        <v>445.097569944684</v>
       </c>
       <c r="O24" t="n">
-        <v>21.12780593071681</v>
+        <v>21.09733561245789</v>
       </c>
       <c r="P24" t="n">
-        <v>438.4063961936175</v>
+        <v>438.6189984145861</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -36854,28 +37084,28 @@
         <v>0.0306</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.116710471814448</v>
+        <v>-1.126975031050639</v>
       </c>
       <c r="J25" t="n">
+        <v>300</v>
+      </c>
+      <c r="K25" t="n">
         <v>298</v>
       </c>
-      <c r="K25" t="n">
-        <v>296</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.141629282245627</v>
+        <v>0.1453898357138629</v>
       </c>
       <c r="M25" t="n">
-        <v>16.26764302035291</v>
+        <v>16.21175370143552</v>
       </c>
       <c r="N25" t="n">
-        <v>421.5222038014579</v>
+        <v>419.1334132838266</v>
       </c>
       <c r="O25" t="n">
-        <v>20.53100591304425</v>
+        <v>20.4727480638</v>
       </c>
       <c r="P25" t="n">
-        <v>430.5887318254049</v>
+        <v>430.6953150304458</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -36932,28 +37162,28 @@
         <v>0.0253</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.8305333549657795</v>
+        <v>-0.8328949923101443</v>
       </c>
       <c r="J26" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K26" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0815790898269364</v>
+        <v>0.08299892208044679</v>
       </c>
       <c r="M26" t="n">
-        <v>16.99585874200562</v>
+        <v>16.89401938859084</v>
       </c>
       <c r="N26" t="n">
-        <v>432.2920102954751</v>
+        <v>429.4336225089306</v>
       </c>
       <c r="O26" t="n">
-        <v>20.79163318009134</v>
+        <v>20.72278027941547</v>
       </c>
       <c r="P26" t="n">
-        <v>428.4439981342811</v>
+        <v>428.4685941806067</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -37010,28 +37240,28 @@
         <v>0.0254</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.7732687759484411</v>
+        <v>-0.7869063845483776</v>
       </c>
       <c r="J27" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K27" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="L27" t="n">
-        <v>0.05297393457770216</v>
+        <v>0.05537227440524717</v>
       </c>
       <c r="M27" t="n">
-        <v>19.97255528929029</v>
+        <v>19.90679472012644</v>
       </c>
       <c r="N27" t="n">
-        <v>595.0600488614195</v>
+        <v>591.8785653249593</v>
       </c>
       <c r="O27" t="n">
-        <v>24.39385268590059</v>
+        <v>24.32855452600831</v>
       </c>
       <c r="P27" t="n">
-        <v>417.2894277900876</v>
+        <v>417.4314614432612</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -37092,28 +37322,28 @@
         <v>0.0321</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2944603799251866</v>
+        <v>-0.281807050647486</v>
       </c>
       <c r="J28" t="n">
+        <v>300</v>
+      </c>
+      <c r="K28" t="n">
         <v>298</v>
       </c>
-      <c r="K28" t="n">
-        <v>296</v>
-      </c>
       <c r="L28" t="n">
-        <v>0.006109296020504251</v>
+        <v>0.005667197785641731</v>
       </c>
       <c r="M28" t="n">
-        <v>22.47639022472532</v>
+        <v>22.41068475544112</v>
       </c>
       <c r="N28" t="n">
-        <v>790.187236288573</v>
+        <v>785.5658663301459</v>
       </c>
       <c r="O28" t="n">
-        <v>28.11026923187633</v>
+        <v>28.02794795075348</v>
       </c>
       <c r="P28" t="n">
-        <v>405.2927334280653</v>
+        <v>405.1612913118911</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -37174,28 +37404,28 @@
         <v>0.0261</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.6576114994724558</v>
+        <v>-0.6025306968809401</v>
       </c>
       <c r="J29" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K29" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L29" t="n">
-        <v>0.02025490666979912</v>
+        <v>0.01709428040546324</v>
       </c>
       <c r="M29" t="n">
-        <v>27.58955688920889</v>
+        <v>27.77488934543187</v>
       </c>
       <c r="N29" t="n">
-        <v>1161.267322728516</v>
+        <v>1166.26973877251</v>
       </c>
       <c r="O29" t="n">
-        <v>34.07737259133274</v>
+        <v>34.15069162948988</v>
       </c>
       <c r="P29" t="n">
-        <v>423.3224918117478</v>
+        <v>422.7457190252222</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -37256,28 +37486,28 @@
         <v>0.0271</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4282046129765384</v>
+        <v>-0.3487435146294713</v>
       </c>
       <c r="J30" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K30" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="L30" t="n">
-        <v>0.008206404890401919</v>
+        <v>0.005412412416323065</v>
       </c>
       <c r="M30" t="n">
-        <v>27.79257431052265</v>
+        <v>28.05323199138836</v>
       </c>
       <c r="N30" t="n">
-        <v>1233.621608737899</v>
+        <v>1252.070980883492</v>
       </c>
       <c r="O30" t="n">
-        <v>35.12294988661828</v>
+        <v>35.38461503087878</v>
       </c>
       <c r="P30" t="n">
-        <v>431.97196806266</v>
+        <v>431.1407483688493</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -37338,28 +37568,28 @@
         <v>0.0304</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4029349737553397</v>
+        <v>-0.311938791895188</v>
       </c>
       <c r="J31" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K31" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L31" t="n">
-        <v>0.006763777900866241</v>
+        <v>0.00401195372483254</v>
       </c>
       <c r="M31" t="n">
-        <v>29.30467599370269</v>
+        <v>29.67774499447989</v>
       </c>
       <c r="N31" t="n">
-        <v>1323.075049099589</v>
+        <v>1349.143564374954</v>
       </c>
       <c r="O31" t="n">
-        <v>36.37409860188414</v>
+        <v>36.73068968008842</v>
       </c>
       <c r="P31" t="n">
-        <v>443.3769095713959</v>
+        <v>442.4238223311536</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -37420,28 +37650,28 @@
         <v>0.0209</v>
       </c>
       <c r="I32" t="n">
-        <v>0.08786387049823763</v>
+        <v>0.1855482103226119</v>
       </c>
       <c r="J32" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K32" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="L32" t="n">
-        <v>0.0003422654742368803</v>
+        <v>0.001496212531841623</v>
       </c>
       <c r="M32" t="n">
-        <v>28.55817367235709</v>
+        <v>28.98719696739422</v>
       </c>
       <c r="N32" t="n">
-        <v>1245.165211750417</v>
+        <v>1276.841909611156</v>
       </c>
       <c r="O32" t="n">
-        <v>35.28689858503319</v>
+        <v>35.73292472791942</v>
       </c>
       <c r="P32" t="n">
-        <v>441.5999655466491</v>
+        <v>440.5713339830961</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -37483,7 +37713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG299"/>
+  <dimension ref="A1:AG301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87125,12 +87355,12 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t>-37.811209026692396,174.831853325309</t>
+          <t>-37.811233785792815,174.83192135212659</t>
         </is>
       </c>
       <c r="T299" t="inlineStr">
         <is>
-          <t>-37.81053116186057,174.8321916968596</t>
+          <t>-37.810559107675466,174.8322615705398</t>
         </is>
       </c>
       <c r="U299" t="inlineStr">
@@ -87194,6 +87424,340 @@
         </is>
       </c>
       <c r="AG299" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:06:17+00:00</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>-37.821429785444636,174.82445766910706</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>-37.82107117972012,174.82524925550865</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>-37.82057078236731,174.82586663057262</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>-37.82004983928742,174.82642243817605</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>-37.819493783594424,174.82693021108972</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>-37.81894004601751,174.8274972013753</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>-37.81836571391971,174.82800525361276</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>-37.81775153088226,174.828416004089</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>-37.817123674466096,174.8288142127388</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>-37.81646067030373,174.82915101621572</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>-37.81582964172465,174.82952238113054</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>-37.815203266978855,174.8299120417861</t>
+        </is>
+      </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>-37.81455772835208,174.83030669967573</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>-37.81389736196906,174.8306411276445</t>
+        </is>
+      </c>
+      <c r="P300" t="inlineStr">
+        <is>
+          <t>-37.813234930480334,174.83096441775</t>
+        </is>
+      </c>
+      <c r="Q300" t="inlineStr">
+        <is>
+          <t>-37.8125555595787,174.83123638187075</t>
+        </is>
+      </c>
+      <c r="R300" t="inlineStr">
+        <is>
+          <t>-37.81189558036045,174.8315658083428</t>
+        </is>
+      </c>
+      <c r="S300" t="inlineStr">
+        <is>
+          <t>-37.8112310807034,174.8319139197559</t>
+        </is>
+      </c>
+      <c r="T300" t="inlineStr">
+        <is>
+          <t>-37.810556592959486,174.8322552829206</t>
+        </is>
+      </c>
+      <c r="U300" t="inlineStr">
+        <is>
+          <t>-37.80990856415062,174.83264056680017</t>
+        </is>
+      </c>
+      <c r="V300" t="inlineStr">
+        <is>
+          <t>-37.809341808028584,174.83328244971804</t>
+        </is>
+      </c>
+      <c r="W300" t="inlineStr">
+        <is>
+          <t>-37.80879239261718,174.83391225983652</t>
+        </is>
+      </c>
+      <c r="X300" t="inlineStr">
+        <is>
+          <t>-37.80825206711492,174.83451650530702</t>
+        </is>
+      </c>
+      <c r="Y300" t="inlineStr">
+        <is>
+          <t>-37.80767188876893,174.8350758937449</t>
+        </is>
+      </c>
+      <c r="Z300" t="inlineStr">
+        <is>
+          <t>-37.80710620887206,174.8356533931901</t>
+        </is>
+      </c>
+      <c r="AA300" t="inlineStr">
+        <is>
+          <t>-37.80672842862727,174.83648354756784</t>
+        </is>
+      </c>
+      <c r="AB300" t="inlineStr">
+        <is>
+          <t>-37.806173206193144,174.83717073533344</t>
+        </is>
+      </c>
+      <c r="AC300" t="inlineStr">
+        <is>
+          <t>-37.805521703590486,174.83781003528358</t>
+        </is>
+      </c>
+      <c r="AD300" t="inlineStr">
+        <is>
+          <t>-37.804969078114,174.83841148300405</t>
+        </is>
+      </c>
+      <c r="AE300" t="inlineStr">
+        <is>
+          <t>-37.80454146178189,174.83890686031762</t>
+        </is>
+      </c>
+      <c r="AF300" t="inlineStr">
+        <is>
+          <t>-37.80406050996268,174.83939388668836</t>
+        </is>
+      </c>
+      <c r="AG300" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:25+00:00</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>-37.821429785444636,174.82445766910706</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>-37.82107117972012,174.82524925550865</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>-37.82057078236731,174.82586663057262</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>-37.82004983928742,174.82642243817605</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>-37.819493783594424,174.82693021108972</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>-37.81894004601751,174.8274972013753</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>-37.81836571391971,174.82800525361276</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>-37.81775153088226,174.828416004089</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>-37.817123674466096,174.8288142127388</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>-37.81646067030373,174.82915101621572</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>-37.81582964172465,174.82952238113054</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>-37.815203266978855,174.8299120417861</t>
+        </is>
+      </c>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>-37.81455772835208,174.83030669967573</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>-37.81389736196906,174.8306411276445</t>
+        </is>
+      </c>
+      <c r="P301" t="inlineStr">
+        <is>
+          <t>-37.813234930480334,174.83096441775</t>
+        </is>
+      </c>
+      <c r="Q301" t="inlineStr">
+        <is>
+          <t>-37.81255320274537,174.83122949982</t>
+        </is>
+      </c>
+      <c r="R301" t="inlineStr">
+        <is>
+          <t>-37.81189255662351,174.83155693888983</t>
+        </is>
+      </c>
+      <c r="S301" t="inlineStr">
+        <is>
+          <t>-37.8112310807034,174.8319139197559</t>
+        </is>
+      </c>
+      <c r="T301" t="inlineStr">
+        <is>
+          <t>-37.810556592959486,174.8322552829206</t>
+        </is>
+      </c>
+      <c r="U301" t="inlineStr">
+        <is>
+          <t>-37.80990856415062,174.83264056680017</t>
+        </is>
+      </c>
+      <c r="V301" t="inlineStr">
+        <is>
+          <t>-37.809341808028584,174.83328244971804</t>
+        </is>
+      </c>
+      <c r="W301" t="inlineStr">
+        <is>
+          <t>-37.80879239261718,174.83391225983652</t>
+        </is>
+      </c>
+      <c r="X301" t="inlineStr">
+        <is>
+          <t>-37.80825206711492,174.83451650530702</t>
+        </is>
+      </c>
+      <c r="Y301" t="inlineStr">
+        <is>
+          <t>-37.80767188876893,174.8350758937449</t>
+        </is>
+      </c>
+      <c r="Z301" t="inlineStr">
+        <is>
+          <t>-37.80710620887206,174.8356533931901</t>
+        </is>
+      </c>
+      <c r="AA301" t="inlineStr">
+        <is>
+          <t>-37.80672842862727,174.83648354756784</t>
+        </is>
+      </c>
+      <c r="AB301" t="inlineStr">
+        <is>
+          <t>-37.806173206193144,174.83717073533344</t>
+        </is>
+      </c>
+      <c r="AC301" t="inlineStr">
+        <is>
+          <t>-37.805521703590486,174.83781003528358</t>
+        </is>
+      </c>
+      <c r="AD301" t="inlineStr">
+        <is>
+          <t>-37.804969078114,174.83841148300405</t>
+        </is>
+      </c>
+      <c r="AE301" t="inlineStr">
+        <is>
+          <t>-37.80454146178189,174.83890686031762</t>
+        </is>
+      </c>
+      <c r="AF301" t="inlineStr">
+        <is>
+          <t>-37.804049257060896,174.8393823483568</t>
+        </is>
+      </c>
+      <c r="AG301" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0228/nzd0228.xlsx
+++ b/data/nzd0228/nzd0228.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG301"/>
+  <dimension ref="A1:AG302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31983,6 +31983,111 @@
         <v>522.4</v>
       </c>
       <c r="AG301" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:57+00:00</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>389.75</v>
+      </c>
+      <c r="C302" t="n">
+        <v>378.82</v>
+      </c>
+      <c r="D302" t="n">
+        <v>386.19</v>
+      </c>
+      <c r="E302" t="n">
+        <v>387.43</v>
+      </c>
+      <c r="F302" t="n">
+        <v>382.37</v>
+      </c>
+      <c r="G302" t="n">
+        <v>371.61</v>
+      </c>
+      <c r="H302" t="n">
+        <v>368.67</v>
+      </c>
+      <c r="I302" t="n">
+        <v>369.53</v>
+      </c>
+      <c r="J302" t="n">
+        <v>372.11</v>
+      </c>
+      <c r="K302" t="n">
+        <v>378.98</v>
+      </c>
+      <c r="L302" t="n">
+        <v>386.72</v>
+      </c>
+      <c r="M302" t="n">
+        <v>378.55</v>
+      </c>
+      <c r="N302" t="n">
+        <v>377.13</v>
+      </c>
+      <c r="O302" t="n">
+        <v>380.39</v>
+      </c>
+      <c r="P302" t="n">
+        <v>387.79</v>
+      </c>
+      <c r="Q302" t="n">
+        <v>397.67</v>
+      </c>
+      <c r="R302" t="n">
+        <v>401.75</v>
+      </c>
+      <c r="S302" t="n">
+        <v>404.91</v>
+      </c>
+      <c r="T302" t="n">
+        <v>413.3</v>
+      </c>
+      <c r="U302" t="n">
+        <v>421.43</v>
+      </c>
+      <c r="V302" t="n">
+        <v>400.5</v>
+      </c>
+      <c r="W302" t="n">
+        <v>387.93</v>
+      </c>
+      <c r="X302" t="n">
+        <v>383.2</v>
+      </c>
+      <c r="Y302" t="n">
+        <v>385.92</v>
+      </c>
+      <c r="Z302" t="n">
+        <v>391.11</v>
+      </c>
+      <c r="AA302" t="n">
+        <v>378.78</v>
+      </c>
+      <c r="AB302" t="n">
+        <v>380.75</v>
+      </c>
+      <c r="AC302" t="n">
+        <v>421.98</v>
+      </c>
+      <c r="AD302" t="n">
+        <v>461.5</v>
+      </c>
+      <c r="AE302" t="n">
+        <v>495.34</v>
+      </c>
+      <c r="AF302" t="n">
+        <v>521.76</v>
+      </c>
+      <c r="AG302" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -31999,7 +32104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B312"/>
+  <dimension ref="A1:B313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35122,6 +35227,16 @@
       </c>
       <c r="B312" t="n">
         <v>0.84</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>
@@ -35290,28 +35405,28 @@
         <v>0.0389</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4475944489565458</v>
+        <v>-0.4522994493589739</v>
       </c>
       <c r="J2" t="n">
+        <v>301</v>
+      </c>
+      <c r="K2" t="n">
         <v>300</v>
       </c>
-      <c r="K2" t="n">
-        <v>299</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.1556201622907137</v>
+        <v>0.1588892063008641</v>
       </c>
       <c r="M2" t="n">
-        <v>5.664472440472491</v>
+        <v>5.665823260264624</v>
       </c>
       <c r="N2" t="n">
-        <v>60.35582106603387</v>
+        <v>60.33623577523314</v>
       </c>
       <c r="O2" t="n">
-        <v>7.768900891762867</v>
+        <v>7.767640296462829</v>
       </c>
       <c r="P2" t="n">
-        <v>409.0161871741466</v>
+        <v>409.0660703955807</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35368,28 +35483,28 @@
         <v>0.0413</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9358259590802642</v>
+        <v>-0.9381502367739563</v>
       </c>
       <c r="J3" t="n">
+        <v>301</v>
+      </c>
+      <c r="K3" t="n">
         <v>300</v>
       </c>
-      <c r="K3" t="n">
-        <v>299</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.3269517274629958</v>
+        <v>0.32944001520373</v>
       </c>
       <c r="M3" t="n">
-        <v>7.772457101595365</v>
+        <v>7.755835697340363</v>
       </c>
       <c r="N3" t="n">
-        <v>100.0991850436171</v>
+        <v>99.80983850709045</v>
       </c>
       <c r="O3" t="n">
-        <v>10.00495802308121</v>
+        <v>9.990487400877418</v>
       </c>
       <c r="P3" t="n">
-        <v>407.2503709513888</v>
+        <v>407.2750133422393</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35446,28 +35561,28 @@
         <v>0.0432</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.073107450213859</v>
+        <v>-1.07271156445929</v>
       </c>
       <c r="J4" t="n">
+        <v>301</v>
+      </c>
+      <c r="K4" t="n">
         <v>300</v>
       </c>
-      <c r="K4" t="n">
-        <v>299</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.3784362569844439</v>
+        <v>0.3798529369077632</v>
       </c>
       <c r="M4" t="n">
-        <v>8.570905814113891</v>
+        <v>8.54425962581672</v>
       </c>
       <c r="N4" t="n">
-        <v>105.0164040330302</v>
+        <v>104.6676350484305</v>
       </c>
       <c r="O4" t="n">
-        <v>10.24775116955082</v>
+        <v>10.23072016274663</v>
       </c>
       <c r="P4" t="n">
-        <v>413.9637089936948</v>
+        <v>413.9595117450085</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35524,28 +35639,28 @@
         <v>0.052</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.33523244876765</v>
+        <v>-1.333158328820679</v>
       </c>
       <c r="J5" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K5" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4525196677818244</v>
+        <v>0.4533506876079915</v>
       </c>
       <c r="M5" t="n">
-        <v>8.608072708024874</v>
+        <v>8.587876511936233</v>
       </c>
       <c r="N5" t="n">
-        <v>119.7888591856796</v>
+        <v>119.423575868369</v>
       </c>
       <c r="O5" t="n">
-        <v>10.94480969161545</v>
+        <v>10.92810943706042</v>
       </c>
       <c r="P5" t="n">
-        <v>419.4933713876549</v>
+        <v>419.4713581115422</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35602,28 +35717,28 @@
         <v>0.0388</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.622198189771356</v>
+        <v>-1.619425873453781</v>
       </c>
       <c r="J6" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K6" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5115608649951644</v>
+        <v>0.5122779690675068</v>
       </c>
       <c r="M6" t="n">
-        <v>9.315530030965261</v>
+        <v>9.299047029878745</v>
       </c>
       <c r="N6" t="n">
-        <v>140.7794012934289</v>
+        <v>140.375534842784</v>
       </c>
       <c r="O6" t="n">
-        <v>11.86504956978389</v>
+        <v>11.84801818207518</v>
       </c>
       <c r="P6" t="n">
-        <v>420.8803818106493</v>
+        <v>420.8511887120623</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35680,28 +35795,28 @@
         <v>0.0433</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.689612740515462</v>
+        <v>-1.690021078442043</v>
       </c>
       <c r="J7" t="n">
+        <v>301</v>
+      </c>
+      <c r="K7" t="n">
         <v>300</v>
       </c>
-      <c r="K7" t="n">
-        <v>299</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.5494517762013194</v>
+        <v>0.5512354700455071</v>
       </c>
       <c r="M7" t="n">
-        <v>9.328964708546449</v>
+        <v>9.299865093166995</v>
       </c>
       <c r="N7" t="n">
-        <v>131.2862336159641</v>
+        <v>130.8500013035632</v>
       </c>
       <c r="O7" t="n">
-        <v>11.45802049291081</v>
+        <v>11.43896854194307</v>
       </c>
       <c r="P7" t="n">
-        <v>416.9659288927465</v>
+        <v>416.9702311122837</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35758,28 +35873,28 @@
         <v>0.036</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.924673795494594</v>
+        <v>-1.929163252962862</v>
       </c>
       <c r="J8" t="n">
+        <v>301</v>
+      </c>
+      <c r="K8" t="n">
         <v>300</v>
       </c>
-      <c r="K8" t="n">
-        <v>299</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.5840245024243638</v>
+        <v>0.5865142982848466</v>
       </c>
       <c r="M8" t="n">
-        <v>9.420100230025596</v>
+        <v>9.415668170726597</v>
       </c>
       <c r="N8" t="n">
-        <v>147.9735477565464</v>
+        <v>147.6481380228166</v>
       </c>
       <c r="O8" t="n">
-        <v>12.16443783150485</v>
+        <v>12.15105501686239</v>
       </c>
       <c r="P8" t="n">
-        <v>426.7283045385707</v>
+        <v>426.7756051451848</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35836,28 +35951,28 @@
         <v>0.0309</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.02222715110317</v>
+        <v>-2.026115834781832</v>
       </c>
       <c r="J9" t="n">
+        <v>301</v>
+      </c>
+      <c r="K9" t="n">
         <v>300</v>
       </c>
-      <c r="K9" t="n">
-        <v>299</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.5400713475924233</v>
+        <v>0.5425373631891972</v>
       </c>
       <c r="M9" t="n">
-        <v>10.45693060003938</v>
+        <v>10.43752996808607</v>
       </c>
       <c r="N9" t="n">
-        <v>195.649724110092</v>
+        <v>195.1236782275049</v>
       </c>
       <c r="O9" t="n">
-        <v>13.98748455263104</v>
+        <v>13.96866773273331</v>
       </c>
       <c r="P9" t="n">
-        <v>429.2174378122832</v>
+        <v>429.2583538687431</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35914,28 +36029,28 @@
         <v>0.0323</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.555737899392523</v>
+        <v>-1.559252387791103</v>
       </c>
       <c r="J10" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K10" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3880969809971966</v>
+        <v>0.3906687034909521</v>
       </c>
       <c r="M10" t="n">
-        <v>10.94641793282073</v>
+        <v>10.92756144885681</v>
       </c>
       <c r="N10" t="n">
-        <v>210.4909422504427</v>
+        <v>209.8850565461302</v>
       </c>
       <c r="O10" t="n">
-        <v>14.50830597452517</v>
+        <v>14.48741027741432</v>
       </c>
       <c r="P10" t="n">
-        <v>418.7694231278981</v>
+        <v>418.8069118585425</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35992,28 +36107,28 @@
         <v>0.0357</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.669517505593832</v>
+        <v>-1.667567914454941</v>
       </c>
       <c r="J11" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K11" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3967490133896112</v>
+        <v>0.3977727719284271</v>
       </c>
       <c r="M11" t="n">
-        <v>11.77007956470472</v>
+        <v>11.74192468086223</v>
       </c>
       <c r="N11" t="n">
-        <v>237.4555301362353</v>
+        <v>236.6982123776015</v>
       </c>
       <c r="O11" t="n">
-        <v>15.40959214697895</v>
+        <v>15.3849995897823</v>
       </c>
       <c r="P11" t="n">
-        <v>420.0568382412748</v>
+        <v>420.0363086191817</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36070,28 +36185,28 @@
         <v>0.0353</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.416016334281562</v>
+        <v>-1.414844604341801</v>
       </c>
       <c r="J12" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K12" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3188453339183905</v>
+        <v>0.3199414780598359</v>
       </c>
       <c r="M12" t="n">
-        <v>11.23691222679082</v>
+        <v>11.20592518161375</v>
       </c>
       <c r="N12" t="n">
-        <v>240.0050307769501</v>
+        <v>239.2190758636055</v>
       </c>
       <c r="O12" t="n">
-        <v>15.49209575160669</v>
+        <v>15.46670863059124</v>
       </c>
       <c r="P12" t="n">
-        <v>422.321712035087</v>
+        <v>422.3093734619479</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36148,28 +36263,28 @@
         <v>0.0347</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.536959908290223</v>
+        <v>-1.537069255236492</v>
       </c>
       <c r="J13" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K13" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3183421649370326</v>
+        <v>0.3198386778792773</v>
       </c>
       <c r="M13" t="n">
-        <v>12.40662358410332</v>
+        <v>12.3659155633645</v>
       </c>
       <c r="N13" t="n">
-        <v>283.4102101982605</v>
+        <v>282.4687473532144</v>
       </c>
       <c r="O13" t="n">
-        <v>16.83479165889084</v>
+        <v>16.80680657808658</v>
       </c>
       <c r="P13" t="n">
-        <v>419.3935634729145</v>
+        <v>419.3947149202305</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36226,28 +36341,28 @@
         <v>0.0368</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.51390093727503</v>
+        <v>-1.514396432213167</v>
       </c>
       <c r="J14" t="n">
+        <v>301</v>
+      </c>
+      <c r="K14" t="n">
         <v>300</v>
       </c>
-      <c r="K14" t="n">
-        <v>299</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.3317762533278249</v>
+        <v>0.3334150410769684</v>
       </c>
       <c r="M14" t="n">
-        <v>12.12538770621442</v>
+        <v>12.08733800755917</v>
       </c>
       <c r="N14" t="n">
-        <v>259.3292830786071</v>
+        <v>258.4668997896293</v>
       </c>
       <c r="O14" t="n">
-        <v>16.10370401735598</v>
+        <v>16.07690579028282</v>
       </c>
       <c r="P14" t="n">
-        <v>417.9734130681999</v>
+        <v>417.9786265801592</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36304,28 +36419,28 @@
         <v>0.0379</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.292409572217632</v>
+        <v>-1.29373408116558</v>
       </c>
       <c r="J15" t="n">
+        <v>301</v>
+      </c>
+      <c r="K15" t="n">
         <v>300</v>
       </c>
-      <c r="K15" t="n">
-        <v>299</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.2892887237237175</v>
+        <v>0.2910850835916712</v>
       </c>
       <c r="M15" t="n">
-        <v>11.37669909508456</v>
+        <v>11.34697341702602</v>
       </c>
       <c r="N15" t="n">
-        <v>230.5377602813144</v>
+        <v>229.7839325534997</v>
       </c>
       <c r="O15" t="n">
-        <v>15.18346996840032</v>
+        <v>15.15862568155503</v>
       </c>
       <c r="P15" t="n">
-        <v>416.6910152736852</v>
+        <v>416.7049515275372</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36382,28 +36497,28 @@
         <v>0.0361</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.081364533728188</v>
+        <v>-1.080939783759698</v>
       </c>
       <c r="J16" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K16" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2540687042811655</v>
+        <v>0.2551934106168624</v>
       </c>
       <c r="M16" t="n">
-        <v>10.19292205843437</v>
+        <v>10.16055556247055</v>
       </c>
       <c r="N16" t="n">
-        <v>194.0018483520529</v>
+        <v>193.352352631553</v>
       </c>
       <c r="O16" t="n">
-        <v>13.9284546289979</v>
+        <v>13.90511965542019</v>
       </c>
       <c r="P16" t="n">
-        <v>415.7215816951119</v>
+        <v>415.7171218277634</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36460,28 +36575,28 @@
         <v>0.0331</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9082001143384971</v>
+        <v>-0.9067793805747255</v>
       </c>
       <c r="J17" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K17" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1868051081751552</v>
+        <v>0.1873421046434113</v>
       </c>
       <c r="M17" t="n">
-        <v>11.06192495136071</v>
+        <v>11.03194965399599</v>
       </c>
       <c r="N17" t="n">
-        <v>201.1810855362664</v>
+        <v>200.5294757528516</v>
       </c>
       <c r="O17" t="n">
-        <v>14.18383183544794</v>
+        <v>14.16084304527282</v>
       </c>
       <c r="P17" t="n">
-        <v>419.441900290971</v>
+        <v>419.4269396529771</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -36538,28 +36653,28 @@
         <v>0.0316</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8207673382361164</v>
+        <v>-0.8175201051361288</v>
       </c>
       <c r="J18" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K18" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1579342098599493</v>
+        <v>0.1577188545463667</v>
       </c>
       <c r="M18" t="n">
-        <v>10.84819449375874</v>
+        <v>10.8274502131546</v>
       </c>
       <c r="N18" t="n">
-        <v>199.47984996245</v>
+        <v>198.8972809200731</v>
       </c>
       <c r="O18" t="n">
-        <v>14.12373357021613</v>
+        <v>14.10309472846556</v>
       </c>
       <c r="P18" t="n">
-        <v>418.3572352101537</v>
+        <v>418.3227248411023</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -36616,28 +36731,28 @@
         <v>0.0318</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.902729304896086</v>
+        <v>-0.8964749744317611</v>
       </c>
       <c r="J19" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K19" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1785774130514223</v>
+        <v>0.1772996153140561</v>
       </c>
       <c r="M19" t="n">
-        <v>11.15311967497474</v>
+        <v>11.14232718555814</v>
       </c>
       <c r="N19" t="n">
-        <v>208.2975590675052</v>
+        <v>207.9170668023131</v>
       </c>
       <c r="O19" t="n">
-        <v>14.43251741961551</v>
+        <v>14.41932962388727</v>
       </c>
       <c r="P19" t="n">
-        <v>418.9641814593315</v>
+        <v>418.8975795566921</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -36694,28 +36809,28 @@
         <v>0.0296</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.317669299020815</v>
+        <v>-1.306879127395327</v>
       </c>
       <c r="J20" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K20" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2689187584729495</v>
+        <v>0.2663042766422038</v>
       </c>
       <c r="M20" t="n">
-        <v>12.51149727456923</v>
+        <v>12.509095817218</v>
       </c>
       <c r="N20" t="n">
-        <v>261.228050056218</v>
+        <v>261.304636692536</v>
       </c>
       <c r="O20" t="n">
-        <v>16.16255085239387</v>
+        <v>16.16491994080193</v>
       </c>
       <c r="P20" t="n">
-        <v>431.2263552593288</v>
+        <v>431.1114464755253</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -36772,28 +36887,28 @@
         <v>0.0268</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5784824870452816</v>
+        <v>-0.569521526431726</v>
       </c>
       <c r="J21" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K21" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L21" t="n">
-        <v>0.05622915605416945</v>
+        <v>0.05483342303409211</v>
       </c>
       <c r="M21" t="n">
-        <v>14.04558304069598</v>
+        <v>14.05090902706532</v>
       </c>
       <c r="N21" t="n">
-        <v>313.8109575866095</v>
+        <v>313.423826018945</v>
       </c>
       <c r="O21" t="n">
-        <v>17.71471020329177</v>
+        <v>17.7037799923899</v>
       </c>
       <c r="P21" t="n">
-        <v>422.577445327391</v>
+        <v>422.4826081970875</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -36850,28 +36965,28 @@
         <v>0.0323</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.358856641739379</v>
+        <v>-1.353430143186908</v>
       </c>
       <c r="J22" t="n">
+        <v>301</v>
+      </c>
+      <c r="K22" t="n">
         <v>300</v>
       </c>
-      <c r="K22" t="n">
-        <v>299</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.2967088903573365</v>
+        <v>0.2962357710253941</v>
       </c>
       <c r="M22" t="n">
-        <v>12.45186538950341</v>
+        <v>12.43946277556033</v>
       </c>
       <c r="N22" t="n">
-        <v>245.8849163582426</v>
+        <v>245.3108939088218</v>
       </c>
       <c r="O22" t="n">
-        <v>15.68071797967946</v>
+        <v>15.66240383558098</v>
       </c>
       <c r="P22" t="n">
-        <v>427.8264818711048</v>
+        <v>427.7693851927683</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -36928,28 +37043,28 @@
         <v>0.0255</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.459858127688876</v>
+        <v>-1.466724814607858</v>
       </c>
       <c r="J23" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K23" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L23" t="n">
-        <v>0.286782363411211</v>
+        <v>0.2898213409765951</v>
       </c>
       <c r="M23" t="n">
-        <v>13.28358279606779</v>
+        <v>13.27710509798253</v>
       </c>
       <c r="N23" t="n">
-        <v>295.85422110785</v>
+        <v>295.2548005430795</v>
       </c>
       <c r="O23" t="n">
-        <v>17.20041339932997</v>
+        <v>17.18297996690561</v>
       </c>
       <c r="P23" t="n">
-        <v>437.4058711179951</v>
+        <v>437.4785023611502</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -37006,28 +37121,28 @@
         <v>0.031</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.456813416220334</v>
+        <v>-1.467582024902166</v>
       </c>
       <c r="J24" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K24" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2101070291272303</v>
+        <v>0.2133519048715663</v>
       </c>
       <c r="M24" t="n">
-        <v>16.20049566697962</v>
+        <v>16.19015869830897</v>
       </c>
       <c r="N24" t="n">
-        <v>445.097569944684</v>
+        <v>444.5494804202945</v>
       </c>
       <c r="O24" t="n">
-        <v>21.09733561245789</v>
+        <v>21.0843420675224</v>
       </c>
       <c r="P24" t="n">
-        <v>438.6189984145861</v>
+        <v>438.7326454578474</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -37084,28 +37199,28 @@
         <v>0.0306</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.126975031050639</v>
+        <v>-1.136465907826474</v>
       </c>
       <c r="J25" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K25" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1453898357138629</v>
+        <v>0.1481235453306656</v>
       </c>
       <c r="M25" t="n">
-        <v>16.21175370143552</v>
+        <v>16.20596276675386</v>
       </c>
       <c r="N25" t="n">
-        <v>419.1334132838266</v>
+        <v>418.4720673940004</v>
       </c>
       <c r="O25" t="n">
-        <v>20.4727480638</v>
+        <v>20.45658982807253</v>
       </c>
       <c r="P25" t="n">
-        <v>430.6953150304458</v>
+        <v>430.7949531550848</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -37162,28 +37277,28 @@
         <v>0.0253</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.8328949923101443</v>
+        <v>-0.8425385934108657</v>
       </c>
       <c r="J26" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K26" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L26" t="n">
-        <v>0.08299892208044679</v>
+        <v>0.08515242442917048</v>
       </c>
       <c r="M26" t="n">
-        <v>16.89401938859084</v>
+        <v>16.88368789425905</v>
       </c>
       <c r="N26" t="n">
-        <v>429.4336225089306</v>
+        <v>428.7794004876816</v>
       </c>
       <c r="O26" t="n">
-        <v>20.72278027941547</v>
+        <v>20.7069891700286</v>
       </c>
       <c r="P26" t="n">
-        <v>428.4685941806067</v>
+        <v>428.5701434143226</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -37240,28 +37355,28 @@
         <v>0.0254</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.7869063845483776</v>
+        <v>-0.7981254329249432</v>
       </c>
       <c r="J27" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K27" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L27" t="n">
-        <v>0.05537227440524717</v>
+        <v>0.05713944009194671</v>
       </c>
       <c r="M27" t="n">
-        <v>19.90679472012644</v>
+        <v>19.89504386477423</v>
       </c>
       <c r="N27" t="n">
-        <v>591.8785653249593</v>
+        <v>590.9576670110642</v>
       </c>
       <c r="O27" t="n">
-        <v>24.32855452600831</v>
+        <v>24.30962087345387</v>
       </c>
       <c r="P27" t="n">
-        <v>417.4314614432612</v>
+        <v>417.5496004821703</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -37322,28 +37437,28 @@
         <v>0.0321</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.281807050647486</v>
+        <v>-0.2924677751635136</v>
       </c>
       <c r="J28" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K28" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L28" t="n">
-        <v>0.005667197785641731</v>
+        <v>0.006134969112566391</v>
       </c>
       <c r="M28" t="n">
-        <v>22.41068475544112</v>
+        <v>22.37802231503384</v>
       </c>
       <c r="N28" t="n">
-        <v>785.5658663301459</v>
+        <v>783.8903642694988</v>
       </c>
       <c r="O28" t="n">
-        <v>28.02794795075348</v>
+        <v>27.99804215064866</v>
       </c>
       <c r="P28" t="n">
-        <v>405.1612913118911</v>
+        <v>405.2732750132115</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -37404,28 +37519,28 @@
         <v>0.0261</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.6025306968809401</v>
+        <v>-0.5929315375691583</v>
       </c>
       <c r="J29" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K29" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L29" t="n">
-        <v>0.01709428040546324</v>
+        <v>0.01666199939476276</v>
       </c>
       <c r="M29" t="n">
-        <v>27.77488934543187</v>
+        <v>27.74626997932523</v>
       </c>
       <c r="N29" t="n">
-        <v>1166.26973877251</v>
+        <v>1163.121624713516</v>
       </c>
       <c r="O29" t="n">
-        <v>34.15069162948988</v>
+        <v>34.10456897123193</v>
       </c>
       <c r="P29" t="n">
-        <v>422.7457190252222</v>
+        <v>422.6440801886435</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -37486,28 +37601,28 @@
         <v>0.0271</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3487435146294713</v>
+        <v>-0.323715345850081</v>
       </c>
       <c r="J30" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K30" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L30" t="n">
-        <v>0.005412412416323065</v>
+        <v>0.004678741165282219</v>
       </c>
       <c r="M30" t="n">
-        <v>28.05323199138836</v>
+        <v>28.0963634321391</v>
       </c>
       <c r="N30" t="n">
-        <v>1252.070980883492</v>
+        <v>1253.078681383454</v>
       </c>
       <c r="O30" t="n">
-        <v>35.38461503087878</v>
+        <v>35.3988514133362</v>
       </c>
       <c r="P30" t="n">
-        <v>431.1407483688493</v>
+        <v>430.8759970616155</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -37568,28 +37683,28 @@
         <v>0.0304</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.311938791895188</v>
+        <v>-0.2732477929463813</v>
       </c>
       <c r="J31" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K31" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L31" t="n">
-        <v>0.00401195372483254</v>
+        <v>0.003073715996476989</v>
       </c>
       <c r="M31" t="n">
-        <v>29.67774499447989</v>
+        <v>29.81733722722782</v>
       </c>
       <c r="N31" t="n">
-        <v>1349.143564374954</v>
+        <v>1357.047155183901</v>
       </c>
       <c r="O31" t="n">
-        <v>36.73068968008842</v>
+        <v>36.83812095077463</v>
       </c>
       <c r="P31" t="n">
-        <v>442.4238223311536</v>
+        <v>442.0140528518801</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -37650,28 +37765,28 @@
         <v>0.0209</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1855482103226119</v>
+        <v>0.2340810639330583</v>
       </c>
       <c r="J32" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K32" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L32" t="n">
-        <v>0.001496212531841623</v>
+        <v>0.002359208650982159</v>
       </c>
       <c r="M32" t="n">
-        <v>28.98719696739422</v>
+        <v>29.20181222382069</v>
       </c>
       <c r="N32" t="n">
-        <v>1276.841909611156</v>
+        <v>1291.989432018913</v>
       </c>
       <c r="O32" t="n">
-        <v>35.73292472791942</v>
+        <v>35.94425450637297</v>
       </c>
       <c r="P32" t="n">
-        <v>440.5713339830961</v>
+        <v>440.0545661051249</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -37713,7 +37828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG301"/>
+  <dimension ref="A1:AG302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87763,6 +87878,173 @@
         </is>
       </c>
     </row>
+    <row r="302">
+      <c r="A302" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:57+00:00</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>-37.82144727575428,174.82447714553265</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>-37.82106101624381,174.82523751391412</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>-37.82054054396571,174.82582780881833</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>-37.82004126858501,174.82640839395503</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>-37.819495166338434,174.82693287123112</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>-37.81896550702913,174.8275446035582</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>-37.81840474214271,174.8280855383669</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>-37.817790982009406,174.8285141885706</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>-37.81714669178422,174.82887675357563</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>-37.81647756474354,174.82919370217917</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>-37.81583771864895,174.82954520016264</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>-37.8152123089003,174.82994124382432</t>
+        </is>
+      </c>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>-37.814561674584176,174.83031828386595</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>-37.81390249000918,174.83065590337762</t>
+        </is>
+      </c>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>-37.8132298574002,174.8309497358352</t>
+        </is>
+      </c>
+      <c r="Q302" t="inlineStr">
+        <is>
+          <t>-37.81254813198133,174.83121469298504</t>
+        </is>
+      </c>
+      <c r="R302" t="inlineStr">
+        <is>
+          <t>-37.81188593997323,174.8315375304423</t>
+        </is>
+      </c>
+      <c r="S302" t="inlineStr">
+        <is>
+          <t>-37.81121699168816,174.83187520950045</t>
+        </is>
+      </c>
+      <c r="T302" t="inlineStr">
+        <is>
+          <t>-37.810535704579415,174.83220305513214</t>
+        </is>
+      </c>
+      <c r="U302" t="inlineStr">
+        <is>
+          <t>-37.80987107203967,174.8325496782813</t>
+        </is>
+      </c>
+      <c r="V302" t="inlineStr">
+        <is>
+          <t>-37.809303102249444,174.83320593874484</t>
+        </is>
+      </c>
+      <c r="W302" t="inlineStr">
+        <is>
+          <t>-37.80878567720097,174.83390157889173</t>
+        </is>
+      </c>
+      <c r="X302" t="inlineStr">
+        <is>
+          <t>-37.808260269373356,174.8345284348031</t>
+        </is>
+      </c>
+      <c r="Y302" t="inlineStr">
+        <is>
+          <t>-37.80771739140632,174.83513417519313</t>
+        </is>
+      </c>
+      <c r="Z302" t="inlineStr">
+        <is>
+          <t>-37.80719534492475,174.8357602032844</t>
+        </is>
+      </c>
+      <c r="AA302" t="inlineStr">
+        <is>
+          <t>-37.80678024869397,174.8365338648148</t>
+        </is>
+      </c>
+      <c r="AB302" t="inlineStr">
+        <is>
+          <t>-37.806387170091945,174.83731665439566</t>
+        </is>
+      </c>
+      <c r="AC302" t="inlineStr">
+        <is>
+          <t>-37.80575122686749,174.83794661889934</t>
+        </is>
+      </c>
+      <c r="AD302" t="inlineStr">
+        <is>
+          <t>-37.80515150843777,174.83853127478633</t>
+        </is>
+      </c>
+      <c r="AE302" t="inlineStr">
+        <is>
+          <t>-37.80461767579909,174.8389728045735</t>
+        </is>
+      </c>
+      <c r="AF302" t="inlineStr">
+        <is>
+          <t>-37.80405373026424,174.83938693502233</t>
+        </is>
+      </c>
+      <c r="AG302" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0228/nzd0228.xlsx
+++ b/data/nzd0228/nzd0228.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG302"/>
+  <dimension ref="A1:AG303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32090,6 +32090,111 @@
       <c r="AG302" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>392.58</v>
+      </c>
+      <c r="C303" t="n">
+        <v>380.36</v>
+      </c>
+      <c r="D303" t="n">
+        <v>386.27</v>
+      </c>
+      <c r="E303" t="n">
+        <v>385.82</v>
+      </c>
+      <c r="F303" t="n">
+        <v>380.48</v>
+      </c>
+      <c r="G303" t="n">
+        <v>371.37</v>
+      </c>
+      <c r="H303" t="n">
+        <v>369.4</v>
+      </c>
+      <c r="I303" t="n">
+        <v>370.19</v>
+      </c>
+      <c r="J303" t="n">
+        <v>371.71</v>
+      </c>
+      <c r="K303" t="n">
+        <v>377.2</v>
+      </c>
+      <c r="L303" t="n">
+        <v>386.72</v>
+      </c>
+      <c r="M303" t="n">
+        <v>378.55</v>
+      </c>
+      <c r="N303" t="n">
+        <v>377.13</v>
+      </c>
+      <c r="O303" t="n">
+        <v>380.39</v>
+      </c>
+      <c r="P303" t="n">
+        <v>387.79</v>
+      </c>
+      <c r="Q303" t="n">
+        <v>397.67</v>
+      </c>
+      <c r="R303" t="n">
+        <v>401.75</v>
+      </c>
+      <c r="S303" t="n">
+        <v>404.91</v>
+      </c>
+      <c r="T303" t="n">
+        <v>413.3</v>
+      </c>
+      <c r="U303" t="n">
+        <v>421.43</v>
+      </c>
+      <c r="V303" t="n">
+        <v>400.5</v>
+      </c>
+      <c r="W303" t="n">
+        <v>387.93</v>
+      </c>
+      <c r="X303" t="n">
+        <v>383.2</v>
+      </c>
+      <c r="Y303" t="n">
+        <v>380.39</v>
+      </c>
+      <c r="Z303" t="n">
+        <v>389.2</v>
+      </c>
+      <c r="AA303" t="n">
+        <v>376.36</v>
+      </c>
+      <c r="AB303" t="n">
+        <v>378.63</v>
+      </c>
+      <c r="AC303" t="n">
+        <v>416.07</v>
+      </c>
+      <c r="AD303" t="n">
+        <v>454.15</v>
+      </c>
+      <c r="AE303" t="n">
+        <v>488.96</v>
+      </c>
+      <c r="AF303" t="n">
+        <v>521.76</v>
+      </c>
+      <c r="AG303" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -32104,7 +32209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B313"/>
+  <dimension ref="A1:B314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35237,6 +35342,16 @@
       </c>
       <c r="B313" t="n">
         <v>0.6</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>0.98</v>
       </c>
     </row>
   </sheetData>
@@ -35405,28 +35520,28 @@
         <v>0.0389</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4522994493589739</v>
+        <v>-0.4551329535422875</v>
       </c>
       <c r="J2" t="n">
+        <v>302</v>
+      </c>
+      <c r="K2" t="n">
         <v>301</v>
       </c>
-      <c r="K2" t="n">
-        <v>300</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.1588892063008641</v>
+        <v>0.161330146406392</v>
       </c>
       <c r="M2" t="n">
-        <v>5.665823260264624</v>
+        <v>5.659310081955407</v>
       </c>
       <c r="N2" t="n">
-        <v>60.33623577523314</v>
+        <v>60.20194458126463</v>
       </c>
       <c r="O2" t="n">
-        <v>7.767640296462829</v>
+        <v>7.75899120899519</v>
       </c>
       <c r="P2" t="n">
-        <v>409.0660703955807</v>
+        <v>409.0962034334443</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35483,28 +35598,28 @@
         <v>0.0413</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9381502367739563</v>
+        <v>-0.9394360037551835</v>
       </c>
       <c r="J3" t="n">
+        <v>302</v>
+      </c>
+      <c r="K3" t="n">
         <v>301</v>
       </c>
-      <c r="K3" t="n">
-        <v>300</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.32944001520373</v>
+        <v>0.3315118122191327</v>
       </c>
       <c r="M3" t="n">
-        <v>7.755835697340363</v>
+        <v>7.735149535368439</v>
       </c>
       <c r="N3" t="n">
-        <v>99.80983850709045</v>
+        <v>99.49186763714941</v>
       </c>
       <c r="O3" t="n">
-        <v>9.990487400877418</v>
+        <v>9.974561024784469</v>
       </c>
       <c r="P3" t="n">
-        <v>407.2750133422393</v>
+        <v>407.2886868936522</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35561,28 +35676,28 @@
         <v>0.0432</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.07271156445929</v>
+        <v>-1.072231804884695</v>
       </c>
       <c r="J4" t="n">
+        <v>302</v>
+      </c>
+      <c r="K4" t="n">
         <v>301</v>
       </c>
-      <c r="K4" t="n">
-        <v>300</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.3798529369077632</v>
+        <v>0.3812315950436389</v>
       </c>
       <c r="M4" t="n">
-        <v>8.54425962581672</v>
+        <v>8.51818106927789</v>
       </c>
       <c r="N4" t="n">
-        <v>104.6676350484305</v>
+        <v>104.3217987666773</v>
       </c>
       <c r="O4" t="n">
-        <v>10.23072016274663</v>
+        <v>10.2138043238882</v>
       </c>
       <c r="P4" t="n">
-        <v>413.9595117450085</v>
+        <v>413.9544097185101</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35639,28 +35754,28 @@
         <v>0.052</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.333158328820679</v>
+        <v>-1.332075993735543</v>
       </c>
       <c r="J5" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K5" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4533506876079915</v>
+        <v>0.4546015613501734</v>
       </c>
       <c r="M5" t="n">
-        <v>8.587876511936233</v>
+        <v>8.56368787371008</v>
       </c>
       <c r="N5" t="n">
-        <v>119.423575868369</v>
+        <v>119.0351659700845</v>
       </c>
       <c r="O5" t="n">
-        <v>10.92810943706042</v>
+        <v>10.91032382517056</v>
       </c>
       <c r="P5" t="n">
-        <v>419.4713581115422</v>
+        <v>419.459835745135</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35717,28 +35832,28 @@
         <v>0.0388</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.619425873453781</v>
+        <v>-1.617805614047295</v>
       </c>
       <c r="J6" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K6" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5122779690675068</v>
+        <v>0.5134221975949691</v>
       </c>
       <c r="M6" t="n">
-        <v>9.299047029878745</v>
+        <v>9.276626908583751</v>
       </c>
       <c r="N6" t="n">
-        <v>140.375534842784</v>
+        <v>139.9326194821575</v>
       </c>
       <c r="O6" t="n">
-        <v>11.84801818207518</v>
+        <v>11.8293118769503</v>
       </c>
       <c r="P6" t="n">
-        <v>420.8511887120623</v>
+        <v>420.8340745636903</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35795,28 +35910,28 @@
         <v>0.0433</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.690021078442043</v>
+        <v>-1.690508690174538</v>
       </c>
       <c r="J7" t="n">
+        <v>302</v>
+      </c>
+      <c r="K7" t="n">
         <v>301</v>
       </c>
-      <c r="K7" t="n">
-        <v>300</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.5512354700455071</v>
+        <v>0.553038073573493</v>
       </c>
       <c r="M7" t="n">
-        <v>9.299865093166995</v>
+        <v>9.271330569549715</v>
       </c>
       <c r="N7" t="n">
-        <v>130.8500013035632</v>
+        <v>130.4172724743962</v>
       </c>
       <c r="O7" t="n">
-        <v>11.43896854194307</v>
+        <v>11.4200381993405</v>
       </c>
       <c r="P7" t="n">
-        <v>416.9702311122837</v>
+        <v>416.9753844207621</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35873,28 +35988,28 @@
         <v>0.036</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.929163252962862</v>
+        <v>-1.93305727533801</v>
       </c>
       <c r="J8" t="n">
+        <v>302</v>
+      </c>
+      <c r="K8" t="n">
         <v>301</v>
       </c>
-      <c r="K8" t="n">
-        <v>300</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.5865142982848466</v>
+        <v>0.5889129761110932</v>
       </c>
       <c r="M8" t="n">
-        <v>9.415668170726597</v>
+        <v>9.407812612766547</v>
       </c>
       <c r="N8" t="n">
-        <v>147.6481380228166</v>
+        <v>147.2844467442092</v>
       </c>
       <c r="O8" t="n">
-        <v>12.15105501686239</v>
+        <v>12.13608036988093</v>
       </c>
       <c r="P8" t="n">
-        <v>426.7756051451848</v>
+        <v>426.8167589919521</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35951,28 +36066,28 @@
         <v>0.0309</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.026115834781832</v>
+        <v>-2.029451097849273</v>
       </c>
       <c r="J9" t="n">
+        <v>302</v>
+      </c>
+      <c r="K9" t="n">
         <v>301</v>
       </c>
-      <c r="K9" t="n">
-        <v>300</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.5425373631891972</v>
+        <v>0.544903964506472</v>
       </c>
       <c r="M9" t="n">
-        <v>10.43752996808607</v>
+        <v>10.41597078060769</v>
       </c>
       <c r="N9" t="n">
-        <v>195.1236782275049</v>
+        <v>194.5686207069643</v>
       </c>
       <c r="O9" t="n">
-        <v>13.96866773273331</v>
+        <v>13.94878563556571</v>
       </c>
       <c r="P9" t="n">
-        <v>429.2583538687431</v>
+        <v>429.2935554353517</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36029,28 +36144,28 @@
         <v>0.0323</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.559252387791103</v>
+        <v>-1.562904376548918</v>
       </c>
       <c r="J10" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K10" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3906687034909521</v>
+        <v>0.3932743384968391</v>
       </c>
       <c r="M10" t="n">
-        <v>10.92756144885681</v>
+        <v>10.90941213678483</v>
       </c>
       <c r="N10" t="n">
-        <v>209.8850565461302</v>
+        <v>209.2920621937865</v>
       </c>
       <c r="O10" t="n">
-        <v>14.48741027741432</v>
+        <v>14.46692995053845</v>
       </c>
       <c r="P10" t="n">
-        <v>418.8069118585425</v>
+        <v>418.8459860898628</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36107,28 +36222,28 @@
         <v>0.0357</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.667567914454941</v>
+        <v>-1.666695759912037</v>
       </c>
       <c r="J11" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K11" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3977727719284271</v>
+        <v>0.3991306806752049</v>
       </c>
       <c r="M11" t="n">
-        <v>11.74192468086223</v>
+        <v>11.70793479973678</v>
       </c>
       <c r="N11" t="n">
-        <v>236.6982123776015</v>
+        <v>235.9207901481994</v>
       </c>
       <c r="O11" t="n">
-        <v>15.3849995897823</v>
+        <v>15.35971321829283</v>
       </c>
       <c r="P11" t="n">
-        <v>420.0363086191817</v>
+        <v>420.0270964015636</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36185,28 +36300,28 @@
         <v>0.0353</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.414844604341801</v>
+        <v>-1.413630865716197</v>
       </c>
       <c r="J12" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K12" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3199414780598359</v>
+        <v>0.3210239230352099</v>
       </c>
       <c r="M12" t="n">
-        <v>11.20592518161375</v>
+        <v>11.17533467624487</v>
       </c>
       <c r="N12" t="n">
-        <v>239.2190758636055</v>
+        <v>238.4392513757646</v>
       </c>
       <c r="O12" t="n">
-        <v>15.46670863059124</v>
+        <v>15.4414782768932</v>
       </c>
       <c r="P12" t="n">
-        <v>422.3093734619479</v>
+        <v>422.2965532290641</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36263,28 +36378,28 @@
         <v>0.0347</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.537069255236492</v>
+        <v>-1.537113778062823</v>
       </c>
       <c r="J13" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K13" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3198386778792773</v>
+        <v>0.3213189846671549</v>
       </c>
       <c r="M13" t="n">
-        <v>12.3659155633645</v>
+        <v>12.3251742352898</v>
       </c>
       <c r="N13" t="n">
-        <v>282.4687473532144</v>
+        <v>281.5334369148447</v>
       </c>
       <c r="O13" t="n">
-        <v>16.80680657808658</v>
+        <v>16.77895815939847</v>
       </c>
       <c r="P13" t="n">
-        <v>419.3947149202305</v>
+        <v>419.395185196936</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36341,28 +36456,28 @@
         <v>0.0368</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.514396432213167</v>
+        <v>-1.514822702346231</v>
       </c>
       <c r="J14" t="n">
+        <v>302</v>
+      </c>
+      <c r="K14" t="n">
         <v>301</v>
       </c>
-      <c r="K14" t="n">
-        <v>300</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.3334150410769684</v>
+        <v>0.335036279079826</v>
       </c>
       <c r="M14" t="n">
-        <v>12.08733800755917</v>
+        <v>12.04922149697963</v>
       </c>
       <c r="N14" t="n">
-        <v>258.4668997896293</v>
+        <v>257.6097280594215</v>
       </c>
       <c r="O14" t="n">
-        <v>16.07690579028282</v>
+        <v>16.05022517161119</v>
       </c>
       <c r="P14" t="n">
-        <v>417.9786265801592</v>
+        <v>417.9831255885368</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36419,28 +36534,28 @@
         <v>0.0379</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.29373408116558</v>
+        <v>-1.294986946347392</v>
       </c>
       <c r="J15" t="n">
+        <v>302</v>
+      </c>
+      <c r="K15" t="n">
         <v>301</v>
       </c>
-      <c r="K15" t="n">
-        <v>300</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.2910850835916712</v>
+        <v>0.2928644385828549</v>
       </c>
       <c r="M15" t="n">
-        <v>11.34697341702602</v>
+        <v>11.31695461234697</v>
       </c>
       <c r="N15" t="n">
-        <v>229.7839325534997</v>
+        <v>229.0336810941258</v>
       </c>
       <c r="O15" t="n">
-        <v>15.15862568155503</v>
+        <v>15.13385876417927</v>
       </c>
       <c r="P15" t="n">
-        <v>416.7049515275372</v>
+        <v>416.7181747175097</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36497,28 +36612,28 @@
         <v>0.0361</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.080939783759698</v>
+        <v>-1.08047646030398</v>
       </c>
       <c r="J16" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K16" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2551934106168624</v>
+        <v>0.2563060222932506</v>
       </c>
       <c r="M16" t="n">
-        <v>10.16055556247055</v>
+        <v>10.12855746937502</v>
       </c>
       <c r="N16" t="n">
-        <v>193.352352631553</v>
+        <v>192.7075025800562</v>
       </c>
       <c r="O16" t="n">
-        <v>13.90511965542019</v>
+        <v>13.88191278534973</v>
       </c>
       <c r="P16" t="n">
-        <v>415.7171218277634</v>
+        <v>415.7122417273341</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36575,28 +36690,28 @@
         <v>0.0331</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9067793805747255</v>
+        <v>-0.9053410197025226</v>
       </c>
       <c r="J17" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K17" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1873421046434113</v>
+        <v>0.1878720628376539</v>
       </c>
       <c r="M17" t="n">
-        <v>11.03194965399599</v>
+        <v>11.00220915415739</v>
       </c>
       <c r="N17" t="n">
-        <v>200.5294757528516</v>
+        <v>199.8827330534439</v>
       </c>
       <c r="O17" t="n">
-        <v>14.16084304527282</v>
+        <v>14.13798900315897</v>
       </c>
       <c r="P17" t="n">
-        <v>419.4269396529771</v>
+        <v>419.4117468256554</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -36653,28 +36768,28 @@
         <v>0.0316</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8175201051361288</v>
+        <v>-0.8142839769367375</v>
       </c>
       <c r="J18" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K18" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1577188545463667</v>
+        <v>0.1575022186952545</v>
       </c>
       <c r="M18" t="n">
-        <v>10.8274502131546</v>
+        <v>10.80668228284492</v>
       </c>
       <c r="N18" t="n">
-        <v>198.8972809200731</v>
+        <v>198.318688494639</v>
       </c>
       <c r="O18" t="n">
-        <v>14.10309472846556</v>
+        <v>14.08256682904928</v>
       </c>
       <c r="P18" t="n">
-        <v>418.3227248411023</v>
+        <v>418.288226641222</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -36731,28 +36846,28 @@
         <v>0.0318</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8964749744317611</v>
+        <v>-0.8902700229219858</v>
       </c>
       <c r="J19" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K19" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1772996153140561</v>
+        <v>0.1760321697698427</v>
       </c>
       <c r="M19" t="n">
-        <v>11.14232718555814</v>
+        <v>11.13119847336344</v>
       </c>
       <c r="N19" t="n">
-        <v>207.9170668023131</v>
+        <v>207.5365282888806</v>
       </c>
       <c r="O19" t="n">
-        <v>14.41932962388727</v>
+        <v>14.40612815050875</v>
       </c>
       <c r="P19" t="n">
-        <v>418.8975795566921</v>
+        <v>418.8312985597688</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -36809,28 +36924,28 @@
         <v>0.0296</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.306879127395327</v>
+        <v>-1.296184586576099</v>
       </c>
       <c r="J20" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K20" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2663042766422038</v>
+        <v>0.2637164713206354</v>
       </c>
       <c r="M20" t="n">
-        <v>12.509095817218</v>
+        <v>12.50616457798576</v>
       </c>
       <c r="N20" t="n">
-        <v>261.304636692536</v>
+        <v>261.3712503548938</v>
       </c>
       <c r="O20" t="n">
-        <v>16.16491994080193</v>
+        <v>16.16698024848468</v>
       </c>
       <c r="P20" t="n">
-        <v>431.1114464755253</v>
+        <v>430.9972070832834</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -36887,28 +37002,28 @@
         <v>0.0268</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.569521526431726</v>
+        <v>-0.5606614018770826</v>
       </c>
       <c r="J21" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K21" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L21" t="n">
-        <v>0.05483342303409211</v>
+        <v>0.05346496759004327</v>
       </c>
       <c r="M21" t="n">
-        <v>14.05090902706532</v>
+        <v>14.05530053537619</v>
       </c>
       <c r="N21" t="n">
-        <v>313.423826018945</v>
+        <v>313.0295037285298</v>
       </c>
       <c r="O21" t="n">
-        <v>17.7037799923899</v>
+        <v>17.69263981797317</v>
       </c>
       <c r="P21" t="n">
-        <v>422.4826081970875</v>
+        <v>422.3885481119538</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -36965,28 +37080,28 @@
         <v>0.0323</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.353430143186908</v>
+        <v>-1.348023223607371</v>
       </c>
       <c r="J22" t="n">
+        <v>302</v>
+      </c>
+      <c r="K22" t="n">
         <v>301</v>
       </c>
-      <c r="K22" t="n">
-        <v>300</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.2962357710253941</v>
+        <v>0.2957610102797243</v>
       </c>
       <c r="M22" t="n">
-        <v>12.43946277556033</v>
+        <v>12.42686259442284</v>
       </c>
       <c r="N22" t="n">
-        <v>245.3108939088218</v>
+        <v>244.7408291729127</v>
       </c>
       <c r="O22" t="n">
-        <v>15.66240383558098</v>
+        <v>15.64419474351149</v>
       </c>
       <c r="P22" t="n">
-        <v>427.7693851927683</v>
+        <v>427.7123186178453</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -37043,28 +37158,28 @@
         <v>0.0255</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.466724814607858</v>
+        <v>-1.473435341095433</v>
       </c>
       <c r="J23" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K23" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2898213409765951</v>
+        <v>0.2928354356798877</v>
       </c>
       <c r="M23" t="n">
-        <v>13.27710509798253</v>
+        <v>13.26976452897107</v>
       </c>
       <c r="N23" t="n">
-        <v>295.2548005430795</v>
+        <v>294.6448067297246</v>
       </c>
       <c r="O23" t="n">
-        <v>17.18297996690561</v>
+        <v>17.16522084710024</v>
       </c>
       <c r="P23" t="n">
-        <v>437.4785023611502</v>
+        <v>437.5497005082977</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -37121,28 +37236,28 @@
         <v>0.031</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.467582024902166</v>
+        <v>-1.478137128395498</v>
       </c>
       <c r="J24" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K24" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2133519048715663</v>
+        <v>0.216576516340424</v>
       </c>
       <c r="M24" t="n">
-        <v>16.19015869830897</v>
+        <v>16.17870669695165</v>
       </c>
       <c r="N24" t="n">
-        <v>444.5494804202945</v>
+        <v>443.9754069971865</v>
       </c>
       <c r="O24" t="n">
-        <v>21.0843420675224</v>
+        <v>21.07072393149287</v>
       </c>
       <c r="P24" t="n">
-        <v>438.7326454578474</v>
+        <v>438.8443796323929</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -37199,28 +37314,28 @@
         <v>0.0306</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.136465907826474</v>
+        <v>-1.149271192798376</v>
       </c>
       <c r="J25" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K25" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1481235453306656</v>
+        <v>0.151433007129705</v>
       </c>
       <c r="M25" t="n">
-        <v>16.20596276675386</v>
+        <v>16.21690630074097</v>
       </c>
       <c r="N25" t="n">
-        <v>418.4720673940004</v>
+        <v>418.4314640348214</v>
       </c>
       <c r="O25" t="n">
-        <v>20.45658982807253</v>
+        <v>20.45559737663072</v>
       </c>
       <c r="P25" t="n">
-        <v>430.7949531550848</v>
+        <v>430.9297992125204</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -37277,28 +37392,28 @@
         <v>0.0253</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.8425385934108657</v>
+        <v>-0.8532093760169965</v>
       </c>
       <c r="J26" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K26" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L26" t="n">
-        <v>0.08515242442917048</v>
+        <v>0.08749390031367255</v>
       </c>
       <c r="M26" t="n">
-        <v>16.88368789425905</v>
+        <v>16.8787386458431</v>
       </c>
       <c r="N26" t="n">
-        <v>428.7794004876816</v>
+        <v>428.3096646742772</v>
       </c>
       <c r="O26" t="n">
-        <v>20.7069891700286</v>
+        <v>20.69564361585011</v>
       </c>
       <c r="P26" t="n">
-        <v>428.5701434143226</v>
+        <v>428.6828545987383</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -37355,28 +37470,28 @@
         <v>0.0254</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.7981254329249432</v>
+        <v>-0.8106719224669812</v>
       </c>
       <c r="J27" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K27" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L27" t="n">
-        <v>0.05713944009194671</v>
+        <v>0.05909380323597346</v>
       </c>
       <c r="M27" t="n">
-        <v>19.89504386477423</v>
+        <v>19.88959284128934</v>
       </c>
       <c r="N27" t="n">
-        <v>590.9576670110642</v>
+        <v>590.3142763677413</v>
       </c>
       <c r="O27" t="n">
-        <v>24.30962087345387</v>
+        <v>24.29638401836251</v>
       </c>
       <c r="P27" t="n">
-        <v>417.5496004821703</v>
+        <v>417.6821240044592</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -37437,28 +37552,28 @@
         <v>0.0321</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2924677751635136</v>
+        <v>-0.304293050367868</v>
       </c>
       <c r="J28" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K28" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L28" t="n">
-        <v>0.006134969112566391</v>
+        <v>0.006672254445003301</v>
       </c>
       <c r="M28" t="n">
-        <v>22.37802231503384</v>
+        <v>22.34988315207124</v>
       </c>
       <c r="N28" t="n">
-        <v>783.8903642694988</v>
+        <v>782.4537766430001</v>
       </c>
       <c r="O28" t="n">
-        <v>27.99804215064866</v>
+        <v>27.97237524135196</v>
       </c>
       <c r="P28" t="n">
-        <v>405.2732750132115</v>
+        <v>405.3978777713471</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -37519,28 +37634,28 @@
         <v>0.0261</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.5929315375691583</v>
+        <v>-0.587167115055978</v>
       </c>
       <c r="J29" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K29" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L29" t="n">
-        <v>0.01666199939476276</v>
+        <v>0.01644936012176024</v>
       </c>
       <c r="M29" t="n">
-        <v>27.74626997932523</v>
+        <v>27.69190107862919</v>
       </c>
       <c r="N29" t="n">
-        <v>1163.121624713516</v>
+        <v>1159.50887081371</v>
       </c>
       <c r="O29" t="n">
-        <v>34.10456897123193</v>
+        <v>34.05156194381852</v>
       </c>
       <c r="P29" t="n">
-        <v>422.6440801886435</v>
+        <v>422.5828556106127</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -37601,28 +37716,28 @@
         <v>0.0271</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.323715345850081</v>
+        <v>-0.3036476176741379</v>
       </c>
       <c r="J30" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K30" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L30" t="n">
-        <v>0.004678741165282219</v>
+        <v>0.004135448008162124</v>
       </c>
       <c r="M30" t="n">
-        <v>28.0963634321391</v>
+        <v>28.11203619851333</v>
       </c>
       <c r="N30" t="n">
-        <v>1253.078681383454</v>
+        <v>1252.246596339797</v>
       </c>
       <c r="O30" t="n">
-        <v>35.3988514133362</v>
+        <v>35.38709646664724</v>
       </c>
       <c r="P30" t="n">
-        <v>430.8759970616155</v>
+        <v>430.6630567610994</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -37683,28 +37798,28 @@
         <v>0.0304</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2732477929463813</v>
+        <v>-0.2390995105196649</v>
       </c>
       <c r="J31" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K31" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L31" t="n">
-        <v>0.003073715996476989</v>
+        <v>0.002354112546869458</v>
       </c>
       <c r="M31" t="n">
-        <v>29.81733722722782</v>
+        <v>29.92795399611168</v>
       </c>
       <c r="N31" t="n">
-        <v>1357.047155183901</v>
+        <v>1362.234506432742</v>
       </c>
       <c r="O31" t="n">
-        <v>36.83812095077463</v>
+        <v>36.90846117671045</v>
       </c>
       <c r="P31" t="n">
-        <v>442.0140528518801</v>
+        <v>441.6512743608596</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -37765,28 +37880,28 @@
         <v>0.0209</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2340810639330583</v>
+        <v>0.2819311604975145</v>
       </c>
       <c r="J32" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K32" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L32" t="n">
-        <v>0.002359208650982159</v>
+        <v>0.003391773735164416</v>
       </c>
       <c r="M32" t="n">
-        <v>29.20181222382069</v>
+        <v>29.40894861396851</v>
       </c>
       <c r="N32" t="n">
-        <v>1291.989432018913</v>
+        <v>1306.639306658354</v>
       </c>
       <c r="O32" t="n">
-        <v>35.94425450637297</v>
+        <v>36.14746611670525</v>
       </c>
       <c r="P32" t="n">
-        <v>440.0545661051249</v>
+        <v>439.5434880275002</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -37828,7 +37943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG302"/>
+  <dimension ref="A1:AG303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88045,6 +88160,173 @@
         </is>
       </c>
     </row>
+    <row r="303">
+      <c r="A303" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>-37.82142816472079,174.8244558643422</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>-37.82105078633828,174.82522569558043</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>-37.8205400389401,174.82582716043856</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>-37.820050113989396,174.82642288831138</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>-37.819504499858866,174.82695082718823</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>-37.818966719457755,174.82754686080582</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>-37.818401305401615,174.82807846865663</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>-37.81778829493842,174.82850750107943</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>-37.81714820857499,174.82888087488416</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>-37.8164847247632,174.82921179290275</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>-37.81583771864895,174.82954520016264</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>-37.8152123089003,174.82994124382432</t>
+        </is>
+      </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>-37.814561674584176,174.83031828386595</t>
+        </is>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>-37.81390249000918,174.83065590337762</t>
+        </is>
+      </c>
+      <c r="P303" t="inlineStr">
+        <is>
+          <t>-37.8132298574002,174.8309497358352</t>
+        </is>
+      </c>
+      <c r="Q303" t="inlineStr">
+        <is>
+          <t>-37.81254813198133,174.83121469298504</t>
+        </is>
+      </c>
+      <c r="R303" t="inlineStr">
+        <is>
+          <t>-37.81188593997323,174.8315375304423</t>
+        </is>
+      </c>
+      <c r="S303" t="inlineStr">
+        <is>
+          <t>-37.81121699168816,174.83187520950045</t>
+        </is>
+      </c>
+      <c r="T303" t="inlineStr">
+        <is>
+          <t>-37.810535704579415,174.83220305513214</t>
+        </is>
+      </c>
+      <c r="U303" t="inlineStr">
+        <is>
+          <t>-37.80987107203967,174.8325496782813</t>
+        </is>
+      </c>
+      <c r="V303" t="inlineStr">
+        <is>
+          <t>-37.809303102249444,174.83320593874484</t>
+        </is>
+      </c>
+      <c r="W303" t="inlineStr">
+        <is>
+          <t>-37.80878567720097,174.83390157889173</t>
+        </is>
+      </c>
+      <c r="X303" t="inlineStr">
+        <is>
+          <t>-37.808260269373356,174.8345284348031</t>
+        </is>
+      </c>
+      <c r="Y303" t="inlineStr">
+        <is>
+          <t>-37.80775233993868,174.83517893863183</t>
+        </is>
+      </c>
+      <c r="Z303" t="inlineStr">
+        <is>
+          <t>-37.80720781743364,174.83577514889322</t>
+        </is>
+      </c>
+      <c r="AA303" t="inlineStr">
+        <is>
+          <t>-37.80679752204425,174.83655063724626</t>
+        </is>
+      </c>
+      <c r="AB303" t="inlineStr">
+        <is>
+          <t>-37.8064039702114,174.8373281117807</t>
+        </is>
+      </c>
+      <c r="AC303" t="inlineStr">
+        <is>
+          <t>-37.80579938028926,174.8379752739322</t>
+        </is>
+      </c>
+      <c r="AD303" t="inlineStr">
+        <is>
+          <t>-37.80521024090324,174.83856984125725</t>
+        </is>
+      </c>
+      <c r="AE303" t="inlineStr">
+        <is>
+          <t>-37.8046650681203,174.8390138109149</t>
+        </is>
+      </c>
+      <c r="AF303" t="inlineStr">
+        <is>
+          <t>-37.80405373026424,174.83938693502233</t>
+        </is>
+      </c>
+      <c r="AG303" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
